--- a/out/C02_automotive_purchase_journey/agent3/agent3_test_cases_for_review.xlsx
+++ b/out/C02_automotive_purchase_journey/agent3/agent3_test_cases_for_review.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K163"/>
+  <dimension ref="A1:K185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6718,30 +6718,244 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
+          <t>Q14</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Q14 | Why was the issue not resolved? | text | — | Show if: Q12 == 'Not resolved'
+Validate: {"min_length": 10, "max_length": 500}</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>TC-4885664620</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q14 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at least 10 characters; the answer must be at most 500 characters</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
+3. S3 = No
+4. S4 = No
+5. Q1 = Auto Brand A
+6. Q2 = Auto Brand A
+7. Q3 = Auto Brand A
+8. Q4 = Initial research
+9. Q5 = Manufacturer website
+10. Q6 = Manufacturer website
+11. Q7 = Very poor
+12. Q8 = 0
+13. Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor...
+14. Q10 = Yes
+15. Q11 = Phone
+16. Q12 = Not resolved</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>At Q14, type a 500-character answer, then submit.</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>Answer rule accepts or rejects</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Q14</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Q14 | Why was the issue not resolved? | text | — | Show if: Q12 == 'Not resolved'
+Validate: {"min_length": 10, "max_length": 500}</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>TC-39c3f76ab7</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q14 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at least 10 characters; the answer must be at most 500 characters</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
+3. S3 = No
+4. S4 = No
+5. Q1 = Auto Brand A
+6. Q2 = Auto Brand A
+7. Q3 = Auto Brand A
+8. Q4 = Initial research
+9. Q5 = Manufacturer website
+10. Q6 = Manufacturer website
+11. Q7 = Very poor
+12. Q8 = 0
+13. Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor...
+14. Q10 = Yes
+15. Q11 = Phone
+16. Q12 = Not resolved</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>At Q14, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>Answer rule accepts or rejects</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Q14</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>Q14 | Why was the issue not resolved? | text | — | Show if: Q12 == 'Not resolved'
+Validate: {"min_length": 10, "max_length": 500}</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>TC-05fb791e04</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q14 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
+3. S3 = No
+4. S4 = No
+5. Q1 = Auto Brand A
+6. Q2 = Auto Brand A
+7. Q3 = Auto Brand A
+8. Q4 = Initial research
+9. Q5 = Manufacturer website
+10. Q6 = Manufacturer website
+11. Q7 = Very poor
+12. Q8 = 0
+13. Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor...
+14. Q10 = Yes
+15. Q11 = Phone
+16. Q12 = Not resolved</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>At Q14, type 3 spaces and nothing else, then submit.</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q14</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>Blank answer is blocked</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>Q15</t>
         </is>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="C96" s="3" t="inlineStr">
         <is>
           <t>Q15 | Have you considered switching providers? | single | Yes; No | Show if: Q3 != 'None/currently not using'</t>
         </is>
       </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>TC-5b4bc2d018</t>
         </is>
       </c>
-      <c r="F93" s="3" t="inlineStr">
+      <c r="F96" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q15: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G93" s="3" t="inlineStr">
+      <c r="G96" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -6773,58 +6987,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H93" s="3" t="inlineStr">
+      <c r="H96" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I93" s="3" t="inlineStr">
+      <c r="I96" s="3" t="inlineStr">
         <is>
           <t>1. Q15 IS shown on the page
 2. the next question shown is Q16</t>
         </is>
       </c>
-      <c r="J93" s="2" t="inlineStr">
+      <c r="J96" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>Q15</t>
         </is>
       </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="C97" s="3" t="inlineStr">
         <is>
           <t>Q15 | Have you considered switching providers? | single | Yes; No | Show if: Q3 != 'None/currently not using'</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>TC-fed888de92</t>
         </is>
       </c>
-      <c r="F94" s="3" t="inlineStr">
+      <c r="F97" s="3" t="inlineStr">
         <is>
           <t>Prove Q15 DOES appear when its condition is met. The QRE says show it if: Q3 != 'None/currently not using'</t>
         </is>
       </c>
-      <c r="G94" s="3" t="inlineStr">
+      <c r="G97" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -6845,57 +7059,57 @@
 17. Q13 = Very low</t>
         </is>
       </c>
-      <c r="H94" s="3" t="inlineStr">
+      <c r="H97" s="3" t="inlineStr">
         <is>
           <t>At Q15, choose “Yes”, then submit.</t>
         </is>
       </c>
-      <c r="I94" s="3" t="inlineStr">
+      <c r="I97" s="3" t="inlineStr">
         <is>
           <t>1. Q15 IS shown on the page</t>
         </is>
       </c>
-      <c r="J94" s="2" t="inlineStr">
+      <c r="J97" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>Q15</t>
         </is>
       </c>
-      <c r="C95" s="3" t="inlineStr">
+      <c r="C98" s="3" t="inlineStr">
         <is>
           <t>Q15 | Have you considered switching providers? | single | Yes; No | Show if: Q3 != 'None/currently not using'</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>TC-08990139ce</t>
         </is>
       </c>
-      <c r="F95" s="3" t="inlineStr">
+      <c r="F98" s="3" t="inlineStr">
         <is>
           <t>Prove Q15 does NOT appear when its condition is not met. The QRE says show it if: Q3 != 'None/currently not using'</t>
         </is>
       </c>
-      <c r="G95" s="3" t="inlineStr">
+      <c r="G98" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -6913,58 +7127,58 @@
 14. Q13 = Very low</t>
         </is>
       </c>
-      <c r="H95" s="3" t="inlineStr">
+      <c r="H98" s="3" t="inlineStr">
         <is>
           <t>After submitting Q13, look for Q15 on the next page. Do not answer it.</t>
         </is>
       </c>
-      <c r="I95" s="3" t="inlineStr">
+      <c r="I98" s="3" t="inlineStr">
         <is>
           <t>1. Q15 is NOT shown on the page
 2. the respondent carries on into the survey rather than being screened out or finished</t>
         </is>
       </c>
-      <c r="J95" s="2" t="inlineStr">
+      <c r="J98" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>Q15</t>
         </is>
       </c>
-      <c r="C96" s="3" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>Q15 | Have you considered switching providers? | single | Yes; No | Show if: Q3 != 'None/currently not using'</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>TC-ca68eda86a</t>
         </is>
       </c>
-      <c r="F96" s="3" t="inlineStr">
+      <c r="F99" s="3" t="inlineStr">
         <is>
           <t>Prove Q15 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G96" s="3" t="inlineStr">
+      <c r="G99" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -6985,59 +7199,59 @@
 17. Q13 = Very low</t>
         </is>
       </c>
-      <c r="H96" s="3" t="inlineStr">
+      <c r="H99" s="3" t="inlineStr">
         <is>
           <t>At Q15, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I96" s="3" t="inlineStr">
+      <c r="I99" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q15</t>
         </is>
       </c>
-      <c r="J96" s="2" t="inlineStr">
+      <c r="J99" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Q16</t>
         </is>
       </c>
-      <c r="C97" s="3" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>Q16 | What is the main reason for considering a switch? | single | Price; Service quality; Features; Poor support; Competitor offer; Other | Show if: Q15 == 'Yes'
 Randomize</t>
         </is>
       </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>TC-21c743eb6a</t>
         </is>
       </c>
-      <c r="F97" s="3" t="inlineStr">
+      <c r="F100" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q16: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G97" s="3" t="inlineStr">
+      <c r="G100" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -7069,59 +7283,59 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H97" s="3" t="inlineStr">
+      <c r="H100" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I97" s="3" t="inlineStr">
+      <c r="I100" s="3" t="inlineStr">
         <is>
           <t>1. Q16 IS shown on the page
 2. the next question shown is Q18_SQ001</t>
         </is>
       </c>
-      <c r="J97" s="2" t="inlineStr">
+      <c r="J100" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>Q16</t>
         </is>
       </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="C101" s="3" t="inlineStr">
         <is>
           <t>Q16 | What is the main reason for considering a switch? | single | Price; Service quality; Features; Poor support; Competitor offer; Other | Show if: Q15 == 'Yes'
 Randomize</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>TC-2111ecce2f</t>
         </is>
       </c>
-      <c r="F98" s="3" t="inlineStr">
+      <c r="F101" s="3" t="inlineStr">
         <is>
           <t>Prove Q16 DOES appear when its condition is met. The QRE says show it if: Q15 == 'Yes'</t>
         </is>
       </c>
-      <c r="G98" s="3" t="inlineStr">
+      <c r="G101" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -7143,58 +7357,58 @@
 18. Q15 = Yes</t>
         </is>
       </c>
-      <c r="H98" s="3" t="inlineStr">
+      <c r="H101" s="3" t="inlineStr">
         <is>
           <t>At Q16, choose “Price”, then submit.</t>
         </is>
       </c>
-      <c r="I98" s="3" t="inlineStr">
+      <c r="I101" s="3" t="inlineStr">
         <is>
           <t>1. Q16 IS shown on the page</t>
         </is>
       </c>
-      <c r="J98" s="2" t="inlineStr">
+      <c r="J101" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>Q16</t>
         </is>
       </c>
-      <c r="C99" s="3" t="inlineStr">
+      <c r="C102" s="3" t="inlineStr">
         <is>
           <t>Q16 | What is the main reason for considering a switch? | single | Price; Service quality; Features; Poor support; Competitor offer; Other | Show if: Q15 == 'Yes'
 Randomize</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>TC-e5efe2e244</t>
         </is>
       </c>
-      <c r="F99" s="3" t="inlineStr">
+      <c r="F102" s="3" t="inlineStr">
         <is>
           <t>Prove Q16 does NOT appear when its condition is not met. The QRE says show it if: Q15 == 'Yes'</t>
         </is>
       </c>
-      <c r="G99" s="3" t="inlineStr">
+      <c r="G102" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -7216,59 +7430,59 @@
 18. Q15 = No</t>
         </is>
       </c>
-      <c r="H99" s="3" t="inlineStr">
+      <c r="H102" s="3" t="inlineStr">
         <is>
           <t>After submitting Q15, look for Q16 on the next page. Do not answer it.</t>
         </is>
       </c>
-      <c r="I99" s="3" t="inlineStr">
+      <c r="I102" s="3" t="inlineStr">
         <is>
           <t>1. Q16 is NOT shown on the page
 2. the respondent carries on into the survey rather than being screened out or finished</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr">
+      <c r="J102" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>Q16</t>
         </is>
       </c>
-      <c r="C100" s="3" t="inlineStr">
+      <c r="C103" s="3" t="inlineStr">
         <is>
           <t>Q16 | What is the main reason for considering a switch? | single | Price; Service quality; Features; Poor support; Competitor offer; Other | Show if: Q15 == 'Yes'
 Randomize</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>TC-1ba7a2b2f4</t>
         </is>
       </c>
-      <c r="F100" s="3" t="inlineStr">
+      <c r="F103" s="3" t="inlineStr">
         <is>
           <t>Prove Q16 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G100" s="3" t="inlineStr">
+      <c r="G103" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -7290,59 +7504,59 @@
 18. Q15 = Yes</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr">
+      <c r="H103" s="3" t="inlineStr">
         <is>
           <t>At Q16, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I100" s="3" t="inlineStr">
+      <c r="I103" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q16</t>
         </is>
       </c>
-      <c r="J100" s="2" t="inlineStr">
+      <c r="J103" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>Q16</t>
         </is>
       </c>
-      <c r="C101" s="3" t="inlineStr">
+      <c r="C104" s="3" t="inlineStr">
         <is>
           <t>Q16 | What is the main reason for considering a switch? | single | Price; Service quality; Features; Poor support; Competitor offer; Other | Show if: Q15 == 'Yes'
 Randomize</t>
         </is>
       </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>TC-99ecbaf9d7</t>
         </is>
       </c>
-      <c r="F101" s="3" t="inlineStr">
+      <c r="F104" s="3" t="inlineStr">
         <is>
           <t>Prove Q16 still shows all 6 of its options when shuffled, with none dropped and none duplicated</t>
         </is>
       </c>
-      <c r="G101" s="3" t="inlineStr">
+      <c r="G104" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -7364,59 +7578,59 @@
 18. Q15 = Yes</t>
         </is>
       </c>
-      <c r="H101" s="3" t="inlineStr">
+      <c r="H104" s="3" t="inlineStr">
         <is>
           <t>At Q16, choose “Price”, then submit.</t>
         </is>
       </c>
-      <c r="I101" s="3" t="inlineStr">
+      <c r="I104" s="3" t="inlineStr">
         <is>
           <t>1. Q16 shows exactly 6 options, none missing and none repeated
 2. the options shown at Q16 are exactly: Competitor offer, Features, Other, Poor support, Price, Service quality</t>
         </is>
       </c>
-      <c r="J101" s="2" t="inlineStr">
+      <c r="J104" s="2" t="inlineStr">
         <is>
           <t>Shuffled options</t>
         </is>
       </c>
-      <c r="K101" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="n">
-        <v>101</v>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>Q16</t>
         </is>
       </c>
-      <c r="C102" s="3" t="inlineStr">
+      <c r="C105" s="3" t="inlineStr">
         <is>
           <t>Q16 | What is the main reason for considering a switch? | single | Price; Service quality; Features; Poor support; Competitor offer; Other | Show if: Q15 == 'Yes'
 Randomize</t>
         </is>
       </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>TC-e519b16991</t>
         </is>
       </c>
-      <c r="F102" s="3" t="inlineStr">
+      <c r="F105" s="3" t="inlineStr">
         <is>
           <t>Prove Q16 is actually shuffled: the option order must differ between respondents. If it never changes, shuffling was not switched on</t>
         </is>
       </c>
-      <c r="G102" s="3" t="inlineStr">
+      <c r="G105" s="3" t="inlineStr">
         <is>
           <t>Run this same path 5 times and record the option order each time, then compare them.
 1. S1 = Yes
@@ -7439,58 +7653,58 @@
 18. Q15 = Yes</t>
         </is>
       </c>
-      <c r="H102" s="3" t="inlineStr">
+      <c r="H105" s="3" t="inlineStr">
         <is>
           <t>At Q16, choose “Price”, then submit.</t>
         </is>
       </c>
-      <c r="I102" s="3" t="inlineStr">
+      <c r="I105" s="3" t="inlineStr">
         <is>
           <t>1. the order the options appear in at Q16 is NOT identical on every run</t>
         </is>
       </c>
-      <c r="J102" s="2" t="inlineStr">
+      <c r="J105" s="2" t="inlineStr">
         <is>
           <t>Shuffled options</t>
         </is>
       </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="n">
-        <v>102</v>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>Q16</t>
         </is>
       </c>
-      <c r="C103" s="3" t="inlineStr">
+      <c r="C106" s="3" t="inlineStr">
         <is>
           <t>Q16 | What is the main reason for considering a switch? | single | Price; Service quality; Features; Poor support; Competitor offer; Other | Show if: Q15 == 'Yes'
 Randomize</t>
         </is>
       </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>TC-5b48946482</t>
         </is>
       </c>
-      <c r="F103" s="3" t="inlineStr">
+      <c r="F106" s="3" t="inlineStr">
         <is>
           <t>Prove Q16 keeps its pinned options in place while the rest shuffle</t>
         </is>
       </c>
-      <c r="G103" s="3" t="inlineStr">
+      <c r="G106" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -7512,58 +7726,58 @@
 18. Q15 = Yes</t>
         </is>
       </c>
-      <c r="H103" s="3" t="inlineStr">
+      <c r="H106" s="3" t="inlineStr">
         <is>
           <t>At Q16, choose “Price”, then submit.</t>
         </is>
       </c>
-      <c r="I103" s="3" t="inlineStr">
+      <c r="I106" s="3" t="inlineStr">
         <is>
           <t>1. anchored options hold position</t>
         </is>
       </c>
-      <c r="J103" s="2" t="inlineStr">
+      <c r="J106" s="2" t="inlineStr">
         <is>
           <t>Shuffled options</t>
         </is>
       </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="n">
-        <v>103</v>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>Q17</t>
         </is>
       </c>
-      <c r="C104" s="3" t="inlineStr">
+      <c r="C107" s="3" t="inlineStr">
         <is>
           <t>Q17 | Please specify the other switching reason. | text | — | Show if: Q16 == 'Other'
 Validate: {"min_length": 3, "max_length": 200}</t>
         </is>
       </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>TC-7d65461215</t>
         </is>
       </c>
-      <c r="F104" s="3" t="inlineStr">
+      <c r="F107" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q17: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G104" s="3" t="inlineStr">
+      <c r="G107" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -7596,59 +7810,59 @@
 29. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H104" s="3" t="inlineStr">
+      <c r="H107" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I104" s="3" t="inlineStr">
+      <c r="I107" s="3" t="inlineStr">
         <is>
           <t>1. Q17 IS shown on the page
 2. the next question shown is Q18_SQ001</t>
         </is>
       </c>
-      <c r="J104" s="2" t="inlineStr">
+      <c r="J107" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K104" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="n">
-        <v>104</v>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>Q17</t>
         </is>
       </c>
-      <c r="C105" s="3" t="inlineStr">
+      <c r="C108" s="3" t="inlineStr">
         <is>
           <t>Q17 | Please specify the other switching reason. | text | — | Show if: Q16 == 'Other'
 Validate: {"min_length": 3, "max_length": 200}</t>
         </is>
       </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>TC-ba1e176a44</t>
         </is>
       </c>
-      <c r="F105" s="3" t="inlineStr">
+      <c r="F108" s="3" t="inlineStr">
         <is>
           <t>Prove Q17 DOES appear when its condition is met. The QRE says show it if: Q16 == 'Other'</t>
         </is>
       </c>
-      <c r="G105" s="3" t="inlineStr">
+      <c r="G108" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -7671,58 +7885,58 @@
 19. Q16 = Other</t>
         </is>
       </c>
-      <c r="H105" s="3" t="inlineStr">
+      <c r="H108" s="3" t="inlineStr">
         <is>
           <t>At Q17, type “xxx”, then submit.</t>
         </is>
       </c>
-      <c r="I105" s="3" t="inlineStr">
+      <c r="I108" s="3" t="inlineStr">
         <is>
           <t>1. Q17 IS shown on the page</t>
         </is>
       </c>
-      <c r="J105" s="2" t="inlineStr">
+      <c r="J108" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K105" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="n">
-        <v>105</v>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>Q17</t>
         </is>
       </c>
-      <c r="C106" s="3" t="inlineStr">
+      <c r="C109" s="3" t="inlineStr">
         <is>
           <t>Q17 | Please specify the other switching reason. | text | — | Show if: Q16 == 'Other'
 Validate: {"min_length": 3, "max_length": 200}</t>
         </is>
       </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>TC-220d2848e3</t>
         </is>
       </c>
-      <c r="F106" s="3" t="inlineStr">
+      <c r="F109" s="3" t="inlineStr">
         <is>
           <t>Prove Q17 does NOT appear when its condition is not met. The QRE says show it if: Q16 == 'Other'</t>
         </is>
       </c>
-      <c r="G106" s="3" t="inlineStr">
+      <c r="G109" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -7745,59 +7959,59 @@
 19. Q16 = Price</t>
         </is>
       </c>
-      <c r="H106" s="3" t="inlineStr">
+      <c r="H109" s="3" t="inlineStr">
         <is>
           <t>After submitting Q16, look for Q17 on the next page. Do not answer it.</t>
         </is>
       </c>
-      <c r="I106" s="3" t="inlineStr">
+      <c r="I109" s="3" t="inlineStr">
         <is>
           <t>1. Q17 is NOT shown on the page
 2. the respondent carries on into the survey rather than being screened out or finished</t>
         </is>
       </c>
-      <c r="J106" s="2" t="inlineStr">
+      <c r="J109" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K106" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="n">
-        <v>106</v>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>Q17</t>
         </is>
       </c>
-      <c r="C107" s="3" t="inlineStr">
+      <c r="C110" s="3" t="inlineStr">
         <is>
           <t>Q17 | Please specify the other switching reason. | text | — | Show if: Q16 == 'Other'
 Validate: {"min_length": 3, "max_length": 200}</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>TC-125b3c2534</t>
         </is>
       </c>
-      <c r="F107" s="3" t="inlineStr">
+      <c r="F110" s="3" t="inlineStr">
         <is>
           <t>Prove Q17 ACCEPTS an answer that obeys its rule. The QRE's rule is: the answer must be at least 3 characters; the answer must be at most 200 characters</t>
         </is>
       </c>
-      <c r="G107" s="3" t="inlineStr">
+      <c r="G110" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -7820,58 +8034,58 @@
 19. Q16 = Other</t>
         </is>
       </c>
-      <c r="H107" s="3" t="inlineStr">
+      <c r="H110" s="3" t="inlineStr">
         <is>
           <t>At Q17, type “xxx”, then submit.</t>
         </is>
       </c>
-      <c r="I107" s="3" t="inlineStr">
+      <c r="I110" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J107" s="2" t="inlineStr">
+      <c r="J110" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K107" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>Q17</t>
         </is>
       </c>
-      <c r="C108" s="3" t="inlineStr">
+      <c r="C111" s="3" t="inlineStr">
         <is>
           <t>Q17 | Please specify the other switching reason. | text | — | Show if: Q16 == 'Other'
 Validate: {"min_length": 3, "max_length": 200}</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>TC-8b10a27e5b</t>
         </is>
       </c>
-      <c r="F108" s="3" t="inlineStr">
+      <c r="F111" s="3" t="inlineStr">
         <is>
           <t>Prove Q17 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at least 3 characters; the answer must be at most 200 characters</t>
         </is>
       </c>
-      <c r="G108" s="3" t="inlineStr">
+      <c r="G111" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -7894,59 +8108,59 @@
 19. Q16 = Other</t>
         </is>
       </c>
-      <c r="H108" s="3" t="inlineStr">
+      <c r="H111" s="3" t="inlineStr">
         <is>
           <t>At Q17, type a 201-character answer, then submit.</t>
         </is>
       </c>
-      <c r="I108" s="3" t="inlineStr">
+      <c r="I111" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q17</t>
         </is>
       </c>
-      <c r="J108" s="2" t="inlineStr">
+      <c r="J111" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K108" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="n">
-        <v>108</v>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>Q17</t>
         </is>
       </c>
-      <c r="C109" s="3" t="inlineStr">
+      <c r="C112" s="3" t="inlineStr">
         <is>
           <t>Q17 | Please specify the other switching reason. | text | — | Show if: Q16 == 'Other'
 Validate: {"min_length": 3, "max_length": 200}</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>TC-0b9a7cfabb</t>
         </is>
       </c>
-      <c r="F109" s="3" t="inlineStr">
+      <c r="F112" s="3" t="inlineStr">
         <is>
           <t>Prove Q17 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question</t>
         </is>
       </c>
-      <c r="G109" s="3" t="inlineStr">
+      <c r="G112" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -7969,58 +8183,281 @@
 19. Q16 = Other</t>
         </is>
       </c>
-      <c r="H109" s="3" t="inlineStr">
+      <c r="H112" s="3" t="inlineStr">
         <is>
           <t>At Q17, type nothing, then submit.</t>
         </is>
       </c>
-      <c r="I109" s="3" t="inlineStr">
+      <c r="I112" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q17</t>
         </is>
       </c>
-      <c r="J109" s="2" t="inlineStr">
+      <c r="J112" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K109" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Q17</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>Q17 | Please specify the other switching reason. | text | — | Show if: Q16 == 'Other'
+Validate: {"min_length": 3, "max_length": 200}</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>TC-c3e04e6d69</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q17 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at least 3 characters; the answer must be at most 200 characters</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
+3. S3 = No
+4. S4 = No
+5. Q1 = Auto Brand A
+6. Q2 = Auto Brand A
+7. Q3 = Auto Brand A
+8. Q4 = Initial research
+9. Q5 = Manufacturer website
+10. Q6 = Manufacturer website
+11. Q7 = Very poor
+12. Q8 = 0
+13. Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor...
+14. Q10 = Yes
+15. Q11 = Phone
+16. Q12 = Fully
+17. Q13 = Very low
+18. Q15 = Yes
+19. Q16 = Other</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>At Q17, type a 200-character answer, then submit.</t>
+        </is>
+      </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>Answer rule accepts or rejects</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Q17</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>Q17 | Please specify the other switching reason. | text | — | Show if: Q16 == 'Other'
+Validate: {"min_length": 3, "max_length": 200}</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>TC-62010da48b</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q17 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at least 3 characters; the answer must be at most 200 characters</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
+3. S3 = No
+4. S4 = No
+5. Q1 = Auto Brand A
+6. Q2 = Auto Brand A
+7. Q3 = Auto Brand A
+8. Q4 = Initial research
+9. Q5 = Manufacturer website
+10. Q6 = Manufacturer website
+11. Q7 = Very poor
+12. Q8 = 0
+13. Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor...
+14. Q10 = Yes
+15. Q11 = Phone
+16. Q12 = Fully
+17. Q13 = Very low
+18. Q15 = Yes
+19. Q16 = Other</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>At Q17, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
+        </is>
+      </c>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>Answer rule accepts or rejects</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Q17</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>Q17 | Please specify the other switching reason. | text | — | Show if: Q16 == 'Other'
+Validate: {"min_length": 3, "max_length": 200}</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>TC-e9d75526e2</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q17 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
+3. S3 = No
+4. S4 = No
+5. Q1 = Auto Brand A
+6. Q2 = Auto Brand A
+7. Q3 = Auto Brand A
+8. Q4 = Initial research
+9. Q5 = Manufacturer website
+10. Q6 = Manufacturer website
+11. Q7 = Very poor
+12. Q8 = 0
+13. Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor...
+14. Q10 = Yes
+15. Q11 = Phone
+16. Q12 = Fully
+17. Q13 = Very low
+18. Q15 = Yes
+19. Q16 = Other</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>At Q17, type 3 spaces and nothing else, then submit.</t>
+        </is>
+      </c>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q17</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>Blank answer is blocked</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>Q18</t>
         </is>
       </c>
-      <c r="C110" s="3" t="inlineStr">
+      <c r="C116" s="3" t="inlineStr">
         <is>
           <t>Q18 | Allocate 100 points across the factors that drive your decision. | constant_sum | Price; Quality; Convenience; Trust; Support | Validate: {"sum": 100}</t>
         </is>
       </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>TC-10edffc232</t>
         </is>
       </c>
-      <c r="F110" s="3" t="inlineStr">
+      <c r="F116" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q18: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G110" s="3" t="inlineStr">
+      <c r="G116" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -8052,58 +8489,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H110" s="3" t="inlineStr">
+      <c r="H116" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I110" s="3" t="inlineStr">
+      <c r="I116" s="3" t="inlineStr">
         <is>
           <t>1. Q18 IS shown on the page
 2. the next question shown is Q19</t>
         </is>
       </c>
-      <c r="J110" s="2" t="inlineStr">
+      <c r="J116" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K110" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>Q18</t>
         </is>
       </c>
-      <c r="C111" s="3" t="inlineStr">
+      <c r="C117" s="3" t="inlineStr">
         <is>
           <t>Q18 | Allocate 100 points across the factors that drive your decision. | constant_sum | Price; Quality; Convenience; Trust; Support | Validate: {"sum": 100}</t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>TC-10f288c00b</t>
         </is>
       </c>
-      <c r="F111" s="3" t="inlineStr">
+      <c r="F117" s="3" t="inlineStr">
         <is>
           <t>Prove Q18 ACCEPTS an answer that obeys its rule. The QRE's rule is: the numbers entered must add up to exactly 100</t>
         </is>
       </c>
-      <c r="G111" s="3" t="inlineStr">
+      <c r="G117" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -8126,57 +8563,57 @@
 19. Q16 = Price</t>
         </is>
       </c>
-      <c r="H111" s="3" t="inlineStr">
+      <c r="H117" s="3" t="inlineStr">
         <is>
           <t>At Q18, fill in every row, then submit.</t>
         </is>
       </c>
-      <c r="I111" s="3" t="inlineStr">
+      <c r="I117" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J111" s="2" t="inlineStr">
+      <c r="J117" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K111" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="n">
-        <v>111</v>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>Q18</t>
         </is>
       </c>
-      <c r="C112" s="3" t="inlineStr">
+      <c r="C118" s="3" t="inlineStr">
         <is>
           <t>Q18 | Allocate 100 points across the factors that drive your decision. | constant_sum | Price; Quality; Convenience; Trust; Support | Validate: {"sum": 100}</t>
         </is>
       </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>TC-e0b1d06bf4</t>
         </is>
       </c>
-      <c r="F112" s="3" t="inlineStr">
+      <c r="F118" s="3" t="inlineStr">
         <is>
           <t>Prove reject rule R18 does NOT fire. The rule is: sum(Q18) != 100  [Same actions as TC-10f288c00b on this question: the questionnaire's answer rule and its compulsory setting come down to the same thing here. Both are kept because they are separate claims, but one run satisfies both.]</t>
         </is>
       </c>
-      <c r="G112" s="3" t="inlineStr">
+      <c r="G118" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -8199,57 +8636,57 @@
 19. Q16 = Price</t>
         </is>
       </c>
-      <c r="H112" s="3" t="inlineStr">
+      <c r="H118" s="3" t="inlineStr">
         <is>
           <t>At Q18, fill in every row, then submit.</t>
         </is>
       </c>
-      <c r="I112" s="3" t="inlineStr">
+      <c r="I118" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J112" s="2" t="inlineStr">
+      <c r="J118" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K112" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>Q18</t>
         </is>
       </c>
-      <c r="C113" s="3" t="inlineStr">
+      <c r="C119" s="3" t="inlineStr">
         <is>
           <t>Q18 | Allocate 100 points across the factors that drive your decision. | constant_sum | Price; Quality; Convenience; Trust; Support | Validate: {"sum": 100}</t>
         </is>
       </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>TC-59337d0674</t>
         </is>
       </c>
-      <c r="F113" s="3" t="inlineStr">
+      <c r="F119" s="3" t="inlineStr">
         <is>
           <t>Prove Q18 REJECTS an answer that breaks its rule. The QRE's rule is: the numbers entered must add up to exactly 100</t>
         </is>
       </c>
-      <c r="G113" s="3" t="inlineStr">
+      <c r="G119" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -8272,58 +8709,58 @@
 19. Q16 = Price</t>
         </is>
       </c>
-      <c r="H113" s="3" t="inlineStr">
+      <c r="H119" s="3" t="inlineStr">
         <is>
           <t>At Q18, fill in every row, then submit.</t>
         </is>
       </c>
-      <c r="I113" s="3" t="inlineStr">
+      <c r="I119" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q18</t>
         </is>
       </c>
-      <c r="J113" s="2" t="inlineStr">
+      <c r="J119" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K113" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="n">
-        <v>113</v>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>Q18</t>
         </is>
       </c>
-      <c r="C114" s="3" t="inlineStr">
+      <c r="C120" s="3" t="inlineStr">
         <is>
           <t>Q18 | Allocate 100 points across the factors that drive your decision. | constant_sum | Price; Quality; Convenience; Trust; Support | Validate: {"sum": 100}</t>
         </is>
       </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>TC-03fd09a67c</t>
         </is>
       </c>
-      <c r="F114" s="3" t="inlineStr">
+      <c r="F120" s="3" t="inlineStr">
         <is>
           <t>Prove reject rule R18 DOES fire. The rule is: sum(Q18) != 100</t>
         </is>
       </c>
-      <c r="G114" s="3" t="inlineStr">
+      <c r="G120" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -8346,58 +8783,58 @@
 19. Q16 = Price</t>
         </is>
       </c>
-      <c r="H114" s="3" t="inlineStr">
+      <c r="H120" s="3" t="inlineStr">
         <is>
           <t>At Q18, fill in every row, then submit.</t>
         </is>
       </c>
-      <c r="I114" s="3" t="inlineStr">
+      <c r="I120" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against R18</t>
         </is>
       </c>
-      <c r="J114" s="2" t="inlineStr">
+      <c r="J120" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K114" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="n">
-        <v>114</v>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>Q18</t>
         </is>
       </c>
-      <c r="C115" s="3" t="inlineStr">
+      <c r="C121" s="3" t="inlineStr">
         <is>
           <t>Q18 | Allocate 100 points across the factors that drive your decision. | constant_sum | Price; Quality; Convenience; Trust; Support | Validate: {"sum": 100}</t>
         </is>
       </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>TC-1ef93dc899</t>
         </is>
       </c>
-      <c r="F115" s="3" t="inlineStr">
+      <c r="F121" s="3" t="inlineStr">
         <is>
           <t>Prove Q18 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a constant_sum question</t>
         </is>
       </c>
-      <c r="G115" s="3" t="inlineStr">
+      <c r="G121" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -8420,59 +8857,59 @@
 19. Q16 = Price</t>
         </is>
       </c>
-      <c r="H115" s="3" t="inlineStr">
+      <c r="H121" s="3" t="inlineStr">
         <is>
           <t>At Q18, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I115" s="3" t="inlineStr">
+      <c r="I121" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q18</t>
         </is>
       </c>
-      <c r="J115" s="2" t="inlineStr">
+      <c r="J121" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K115" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>Q19</t>
         </is>
       </c>
-      <c r="C116" s="3" t="inlineStr">
+      <c r="C122" s="3" t="inlineStr">
         <is>
           <t>Q19 | Which new proposition do you prefer? | single | Concept A; Concept B; Concept C | Randomize
 Concept descriptions are displayed in randomized order; store display order.</t>
         </is>
       </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>TC-88093bffe3</t>
         </is>
       </c>
-      <c r="F116" s="3" t="inlineStr">
+      <c r="F122" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q19: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G116" s="3" t="inlineStr">
+      <c r="G122" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -8504,59 +8941,59 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H116" s="3" t="inlineStr">
+      <c r="H122" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I116" s="3" t="inlineStr">
+      <c r="I122" s="3" t="inlineStr">
         <is>
           <t>1. Q19 IS shown on the page
 2. the next question shown is Q20</t>
         </is>
       </c>
-      <c r="J116" s="2" t="inlineStr">
+      <c r="J122" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K116" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="n">
-        <v>116</v>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>Q19</t>
         </is>
       </c>
-      <c r="C117" s="3" t="inlineStr">
+      <c r="C123" s="3" t="inlineStr">
         <is>
           <t>Q19 | Which new proposition do you prefer? | single | Concept A; Concept B; Concept C | Randomize
 Concept descriptions are displayed in randomized order; store display order.</t>
         </is>
       </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>TC-60b738ceb3</t>
         </is>
       </c>
-      <c r="F117" s="3" t="inlineStr">
+      <c r="F123" s="3" t="inlineStr">
         <is>
           <t>Prove Q19 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G117" s="3" t="inlineStr">
+      <c r="G123" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -8580,59 +9017,59 @@
 20. Q18 = Price=20; Quality=20; Convenience=20...</t>
         </is>
       </c>
-      <c r="H117" s="3" t="inlineStr">
+      <c r="H123" s="3" t="inlineStr">
         <is>
           <t>At Q19, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I117" s="3" t="inlineStr">
+      <c r="I123" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q19</t>
         </is>
       </c>
-      <c r="J117" s="2" t="inlineStr">
+      <c r="J123" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K117" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="n">
-        <v>117</v>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>Q19</t>
         </is>
       </c>
-      <c r="C118" s="3" t="inlineStr">
+      <c r="C124" s="3" t="inlineStr">
         <is>
           <t>Q19 | Which new proposition do you prefer? | single | Concept A; Concept B; Concept C | Randomize
 Concept descriptions are displayed in randomized order; store display order.</t>
         </is>
       </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>TC-7c2129fe6f</t>
         </is>
       </c>
-      <c r="F118" s="3" t="inlineStr">
+      <c r="F124" s="3" t="inlineStr">
         <is>
           <t>Prove Q19 still shows all 3 of its options when shuffled, with none dropped and none duplicated</t>
         </is>
       </c>
-      <c r="G118" s="3" t="inlineStr">
+      <c r="G124" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -8656,59 +9093,59 @@
 20. Q18 = Price=20; Quality=20; Convenience=20...</t>
         </is>
       </c>
-      <c r="H118" s="3" t="inlineStr">
+      <c r="H124" s="3" t="inlineStr">
         <is>
           <t>At Q19, choose “Concept A”, then submit.</t>
         </is>
       </c>
-      <c r="I118" s="3" t="inlineStr">
+      <c r="I124" s="3" t="inlineStr">
         <is>
           <t>1. Q19 shows exactly 3 options, none missing and none repeated
 2. the options shown at Q19 are exactly: Concept A, Concept B, Concept C</t>
         </is>
       </c>
-      <c r="J118" s="2" t="inlineStr">
+      <c r="J124" s="2" t="inlineStr">
         <is>
           <t>Shuffled options</t>
         </is>
       </c>
-      <c r="K118" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="n">
-        <v>118</v>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>Q19</t>
         </is>
       </c>
-      <c r="C119" s="3" t="inlineStr">
+      <c r="C125" s="3" t="inlineStr">
         <is>
           <t>Q19 | Which new proposition do you prefer? | single | Concept A; Concept B; Concept C | Randomize
 Concept descriptions are displayed in randomized order; store display order.</t>
         </is>
       </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>TC-6789ff4e74</t>
         </is>
       </c>
-      <c r="F119" s="3" t="inlineStr">
+      <c r="F125" s="3" t="inlineStr">
         <is>
           <t>Prove Q19 is actually shuffled: the option order must differ between respondents. If it never changes, shuffling was not switched on</t>
         </is>
       </c>
-      <c r="G119" s="3" t="inlineStr">
+      <c r="G125" s="3" t="inlineStr">
         <is>
           <t>Run this same path 5 times and record the option order each time, then compare them.
 1. S1 = Yes
@@ -8733,57 +9170,57 @@
 20. Q18 = Price=20; Quality=20; Convenience=20...</t>
         </is>
       </c>
-      <c r="H119" s="3" t="inlineStr">
+      <c r="H125" s="3" t="inlineStr">
         <is>
           <t>At Q19, choose “Concept A”, then submit.</t>
         </is>
       </c>
-      <c r="I119" s="3" t="inlineStr">
+      <c r="I125" s="3" t="inlineStr">
         <is>
           <t>1. the order the options appear in at Q19 is NOT identical on every run</t>
         </is>
       </c>
-      <c r="J119" s="2" t="inlineStr">
+      <c r="J125" s="2" t="inlineStr">
         <is>
           <t>Shuffled options</t>
         </is>
       </c>
-      <c r="K119" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>Q20</t>
         </is>
       </c>
-      <c r="C120" s="3" t="inlineStr">
+      <c r="C126" s="3" t="inlineStr">
         <is>
           <t>Q20 | How appealing is the selected proposition? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
         </is>
       </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>TC-a892eef1e4</t>
         </is>
       </c>
-      <c r="F120" s="3" t="inlineStr">
+      <c r="F126" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q20: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G120" s="3" t="inlineStr">
+      <c r="G126" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -8815,58 +9252,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H120" s="3" t="inlineStr">
+      <c r="H126" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I120" s="3" t="inlineStr">
+      <c r="I126" s="3" t="inlineStr">
         <is>
           <t>1. Q20 IS shown on the page
 2. the next question shown is Q21</t>
         </is>
       </c>
-      <c r="J120" s="2" t="inlineStr">
+      <c r="J126" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K120" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>Q20</t>
         </is>
       </c>
-      <c r="C121" s="3" t="inlineStr">
+      <c r="C127" s="3" t="inlineStr">
         <is>
           <t>Q20 | How appealing is the selected proposition? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
         </is>
       </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>TC-a90db4cc87</t>
         </is>
       </c>
-      <c r="F121" s="3" t="inlineStr">
+      <c r="F127" s="3" t="inlineStr">
         <is>
           <t>Prove Q20 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G121" s="3" t="inlineStr">
+      <c r="G127" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -8891,58 +9328,58 @@
 21. Q19 = Concept A</t>
         </is>
       </c>
-      <c r="H121" s="3" t="inlineStr">
+      <c r="H127" s="3" t="inlineStr">
         <is>
           <t>At Q20, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I121" s="3" t="inlineStr">
+      <c r="I127" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q20</t>
         </is>
       </c>
-      <c r="J121" s="2" t="inlineStr">
+      <c r="J127" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K121" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="n">
-        <v>121</v>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>Q20</t>
         </is>
       </c>
-      <c r="C122" s="3" t="inlineStr">
+      <c r="C128" s="3" t="inlineStr">
         <is>
           <t>Q20 | How appealing is the selected proposition? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
         </is>
       </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>TC-cc22176bcb</t>
         </is>
       </c>
-      <c r="F122" s="3" t="inlineStr">
+      <c r="F128" s="3" t="inlineStr">
         <is>
           <t>Q20's wording comes from Q19's answer: the earlier answer should appear in the wording</t>
         </is>
       </c>
-      <c r="G122" s="3" t="inlineStr">
+      <c r="G128" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -8967,57 +9404,57 @@
 21. Q19 = Concept A</t>
         </is>
       </c>
-      <c r="H122" s="3" t="inlineStr">
+      <c r="H128" s="3" t="inlineStr">
         <is>
           <t>At Q20, choose “Very poor”, then submit.</t>
         </is>
       </c>
-      <c r="I122" s="3" t="inlineStr">
+      <c r="I128" s="3" t="inlineStr">
         <is>
           <t>1. Q20's wording includes the words: Concept A</t>
         </is>
       </c>
-      <c r="J122" s="2" t="inlineStr">
+      <c r="J128" s="2" t="inlineStr">
         <is>
           <t>Wording carried forward</t>
         </is>
       </c>
-      <c r="K122" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="n">
-        <v>122</v>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>Q21</t>
         </is>
       </c>
-      <c r="C123" s="3" t="inlineStr">
+      <c r="C129" s="3" t="inlineStr">
         <is>
           <t>Q21 | What most influenced your choice? | text | — | Validate: {"min_length": 5, "max_length": 500}</t>
         </is>
       </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>TC-5b2db56449</t>
         </is>
       </c>
-      <c r="F123" s="3" t="inlineStr">
+      <c r="F129" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q21: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G123" s="3" t="inlineStr">
+      <c r="G129" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -9049,58 +9486,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H123" s="3" t="inlineStr">
+      <c r="H129" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I123" s="3" t="inlineStr">
+      <c r="I129" s="3" t="inlineStr">
         <is>
           <t>1. Q21 IS shown on the page
 2. the next question shown is D1</t>
         </is>
       </c>
-      <c r="J123" s="2" t="inlineStr">
+      <c r="J129" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K123" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="n">
-        <v>123</v>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>Q21</t>
         </is>
       </c>
-      <c r="C124" s="3" t="inlineStr">
+      <c r="C130" s="3" t="inlineStr">
         <is>
           <t>Q21 | What most influenced your choice? | text | — | Validate: {"min_length": 5, "max_length": 500}</t>
         </is>
       </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>TC-a8fcf8afbe</t>
         </is>
       </c>
-      <c r="F124" s="3" t="inlineStr">
+      <c r="F130" s="3" t="inlineStr">
         <is>
           <t>Prove Q21 ACCEPTS an answer that obeys its rule. The QRE's rule is: the answer must be at least 5 characters; the answer must be at most 500 characters</t>
         </is>
       </c>
-      <c r="G124" s="3" t="inlineStr">
+      <c r="G130" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -9126,57 +9563,57 @@
 22. Q20 = Very poor</t>
         </is>
       </c>
-      <c r="H124" s="3" t="inlineStr">
+      <c r="H130" s="3" t="inlineStr">
         <is>
           <t>At Q21, type “xxxxx”, then submit.</t>
         </is>
       </c>
-      <c r="I124" s="3" t="inlineStr">
+      <c r="I130" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J124" s="2" t="inlineStr">
+      <c r="J130" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K124" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="n">
-        <v>124</v>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>Q21</t>
         </is>
       </c>
-      <c r="C125" s="3" t="inlineStr">
+      <c r="C131" s="3" t="inlineStr">
         <is>
           <t>Q21 | What most influenced your choice? | text | — | Validate: {"min_length": 5, "max_length": 500}</t>
         </is>
       </c>
-      <c r="D125" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>TC-5c326b3c25</t>
         </is>
       </c>
-      <c r="F125" s="3" t="inlineStr">
+      <c r="F131" s="3" t="inlineStr">
         <is>
           <t>Prove Q21 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at least 5 characters; the answer must be at most 500 characters</t>
         </is>
       </c>
-      <c r="G125" s="3" t="inlineStr">
+      <c r="G131" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -9202,58 +9639,58 @@
 22. Q20 = Very poor</t>
         </is>
       </c>
-      <c r="H125" s="3" t="inlineStr">
+      <c r="H131" s="3" t="inlineStr">
         <is>
           <t>At Q21, type a 501-character answer, then submit.</t>
         </is>
       </c>
-      <c r="I125" s="3" t="inlineStr">
+      <c r="I131" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q21</t>
         </is>
       </c>
-      <c r="J125" s="2" t="inlineStr">
+      <c r="J131" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K125" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="n">
-        <v>125</v>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>Q21</t>
         </is>
       </c>
-      <c r="C126" s="3" t="inlineStr">
+      <c r="C132" s="3" t="inlineStr">
         <is>
           <t>Q21 | What most influenced your choice? | text | — | Validate: {"min_length": 5, "max_length": 500}</t>
         </is>
       </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>TC-a59227b46e</t>
         </is>
       </c>
-      <c r="F126" s="3" t="inlineStr">
+      <c r="F132" s="3" t="inlineStr">
         <is>
           <t>Prove Q21 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question</t>
         </is>
       </c>
-      <c r="G126" s="3" t="inlineStr">
+      <c r="G132" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -9279,58 +9716,58 @@
 22. Q20 = Very poor</t>
         </is>
       </c>
-      <c r="H126" s="3" t="inlineStr">
+      <c r="H132" s="3" t="inlineStr">
         <is>
           <t>At Q21, type nothing, then submit.</t>
         </is>
       </c>
-      <c r="I126" s="3" t="inlineStr">
+      <c r="I132" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q21</t>
         </is>
       </c>
-      <c r="J126" s="2" t="inlineStr">
+      <c r="J132" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K126" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="n">
-        <v>126</v>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>Q21</t>
         </is>
       </c>
-      <c r="C127" s="3" t="inlineStr">
+      <c r="C133" s="3" t="inlineStr">
         <is>
           <t>Q21 | What most influenced your choice? | text | — | Validate: {"min_length": 5, "max_length": 500}</t>
         </is>
       </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>TC-42363fd1b9</t>
         </is>
       </c>
-      <c r="F127" s="3" t="inlineStr">
+      <c r="F133" s="3" t="inlineStr">
         <is>
           <t>Q21's wording comes from Q19's answer: the earlier answer should appear in the wording</t>
         </is>
       </c>
-      <c r="G127" s="3" t="inlineStr">
+      <c r="G133" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -9356,57 +9793,286 @@
 22. Q20 = Very poor</t>
         </is>
       </c>
-      <c r="H127" s="3" t="inlineStr">
+      <c r="H133" s="3" t="inlineStr">
         <is>
           <t>At Q21, type “xxxxx”, then submit.</t>
         </is>
       </c>
-      <c r="I127" s="3" t="inlineStr">
+      <c r="I133" s="3" t="inlineStr">
         <is>
           <t>1. Q21's wording includes the words: Concept A</t>
         </is>
       </c>
-      <c r="J127" s="2" t="inlineStr">
+      <c r="J133" s="2" t="inlineStr">
         <is>
           <t>Wording carried forward</t>
         </is>
       </c>
-      <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="n">
-        <v>127</v>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Q21</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>Q21 | What most influenced your choice? | text | — | Validate: {"min_length": 5, "max_length": 500}</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>TC-524d7f1984</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q21 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at least 5 characters; the answer must be at most 500 characters</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
+3. S3 = No
+4. S4 = No
+5. Q1 = Auto Brand A
+6. Q2 = Auto Brand A
+7. Q3 = Auto Brand A
+8. Q4 = Initial research
+9. Q5 = Manufacturer website
+10. Q6 = Manufacturer website
+11. Q7 = Very poor
+12. Q8 = 0
+13. Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor...
+14. Q10 = Yes
+15. Q11 = Phone
+16. Q12 = Fully
+17. Q13 = Very low
+18. Q15 = Yes
+19. Q16 = Price
+20. Q18 = Price=20; Quality=20; Convenience=20...
+21. Q19 = Concept A
+22. Q20 = Very poor</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>At Q21, type a 500-character answer, then submit.</t>
+        </is>
+      </c>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>Answer rule accepts or rejects</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Q21</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>Q21 | What most influenced your choice? | text | — | Validate: {"min_length": 5, "max_length": 500}</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>TC-8aaf18bb07</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q21 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at least 5 characters; the answer must be at most 500 characters</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
+3. S3 = No
+4. S4 = No
+5. Q1 = Auto Brand A
+6. Q2 = Auto Brand A
+7. Q3 = Auto Brand A
+8. Q4 = Initial research
+9. Q5 = Manufacturer website
+10. Q6 = Manufacturer website
+11. Q7 = Very poor
+12. Q8 = 0
+13. Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor...
+14. Q10 = Yes
+15. Q11 = Phone
+16. Q12 = Fully
+17. Q13 = Very low
+18. Q15 = Yes
+19. Q16 = Price
+20. Q18 = Price=20; Quality=20; Convenience=20...
+21. Q19 = Concept A
+22. Q20 = Very poor</t>
+        </is>
+      </c>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>At Q21, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
+        </is>
+      </c>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
+          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>Answer rule accepts or rejects</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Q21</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>Q21 | What most influenced your choice? | text | — | Validate: {"min_length": 5, "max_length": 500}</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>TC-2b316ac481</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q21 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
+3. S3 = No
+4. S4 = No
+5. Q1 = Auto Brand A
+6. Q2 = Auto Brand A
+7. Q3 = Auto Brand A
+8. Q4 = Initial research
+9. Q5 = Manufacturer website
+10. Q6 = Manufacturer website
+11. Q7 = Very poor
+12. Q8 = 0
+13. Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor...
+14. Q10 = Yes
+15. Q11 = Phone
+16. Q12 = Fully
+17. Q13 = Very low
+18. Q15 = Yes
+19. Q16 = Price
+20. Q18 = Price=20; Quality=20; Convenience=20...
+21. Q19 = Concept A
+22. Q20 = Very poor</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>At Q21, type 3 spaces and nothing else, then submit.</t>
+        </is>
+      </c>
+      <c r="I136" s="3" t="inlineStr">
+        <is>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q21</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>Blank answer is blocked</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C128" s="3" t="inlineStr">
+      <c r="C137" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>TC-9d345eef73</t>
         </is>
       </c>
-      <c r="F128" s="3" t="inlineStr">
+      <c r="F137" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at D1: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G128" s="3" t="inlineStr">
+      <c r="G137" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -9438,58 +10104,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H128" s="3" t="inlineStr">
+      <c r="H137" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I128" s="3" t="inlineStr">
+      <c r="I137" s="3" t="inlineStr">
         <is>
           <t>1. D1 IS shown on the page
 2. the next question shown is D2</t>
         </is>
       </c>
-      <c r="J128" s="2" t="inlineStr">
+      <c r="J137" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K128" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="n">
-        <v>128</v>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C129" s="3" t="inlineStr">
+      <c r="C138" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>TC-eba66f169b</t>
         </is>
       </c>
-      <c r="F129" s="3" t="inlineStr">
+      <c r="F138" s="3" t="inlineStr">
         <is>
           <t>Prove D1 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G129" s="3" t="inlineStr">
+      <c r="G138" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -9516,58 +10182,58 @@
 23. Q21 = xxxxx</t>
         </is>
       </c>
-      <c r="H129" s="3" t="inlineStr">
+      <c r="H138" s="3" t="inlineStr">
         <is>
           <t>At D1, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I129" s="3" t="inlineStr">
+      <c r="I138" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against D1</t>
         </is>
       </c>
-      <c r="J129" s="2" t="inlineStr">
+      <c r="J138" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K129" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="n">
-        <v>129</v>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C130" s="3" t="inlineStr">
+      <c r="C139" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>TC-640f339984</t>
         </is>
       </c>
-      <c r="F130" s="3" t="inlineStr">
+      <c r="F139" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION lets a 'North' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G130" s="3" t="inlineStr">
+      <c r="G139" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -9594,57 +10260,57 @@
 23. Q21 = xxxxx</t>
         </is>
       </c>
-      <c r="H130" s="3" t="inlineStr">
+      <c r="H139" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “North”, then submit.</t>
         </is>
       </c>
-      <c r="I130" s="3" t="inlineStr">
+      <c r="I139" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J130" s="2" t="inlineStr">
+      <c r="J139" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K130" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="n">
-        <v>130</v>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C131" s="3" t="inlineStr">
+      <c r="C140" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>TC-6a4f70dee1</t>
         </is>
       </c>
-      <c r="F131" s="3" t="inlineStr">
+      <c r="F140" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION lets a 'South' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G131" s="3" t="inlineStr">
+      <c r="G140" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -9671,57 +10337,57 @@
 23. Q21 = xxxxx</t>
         </is>
       </c>
-      <c r="H131" s="3" t="inlineStr">
+      <c r="H140" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “South”, then submit.</t>
         </is>
       </c>
-      <c r="I131" s="3" t="inlineStr">
+      <c r="I140" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J131" s="2" t="inlineStr">
+      <c r="J140" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K131" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="n">
-        <v>131</v>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C132" s="3" t="inlineStr">
+      <c r="C141" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>TC-add22f59a7</t>
         </is>
       </c>
-      <c r="F132" s="3" t="inlineStr">
+      <c r="F141" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION lets a 'East' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G132" s="3" t="inlineStr">
+      <c r="G141" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -9748,57 +10414,57 @@
 23. Q21 = xxxxx</t>
         </is>
       </c>
-      <c r="H132" s="3" t="inlineStr">
+      <c r="H141" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “East”, then submit.</t>
         </is>
       </c>
-      <c r="I132" s="3" t="inlineStr">
+      <c r="I141" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J132" s="2" t="inlineStr">
+      <c r="J141" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K132" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C133" s="3" t="inlineStr">
+      <c r="C142" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D133" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>TC-e3f1efd2fe</t>
         </is>
       </c>
-      <c r="F133" s="3" t="inlineStr">
+      <c r="F142" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION lets a 'West' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G133" s="3" t="inlineStr">
+      <c r="G142" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -9825,57 +10491,57 @@
 23. Q21 = xxxxx</t>
         </is>
       </c>
-      <c r="H133" s="3" t="inlineStr">
+      <c r="H142" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “West”, then submit.</t>
         </is>
       </c>
-      <c r="I133" s="3" t="inlineStr">
+      <c r="I142" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J133" s="2" t="inlineStr">
+      <c r="J142" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K133" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="n">
-        <v>133</v>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C134" s="3" t="inlineStr">
+      <c r="C143" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>TC-faf234994c</t>
         </is>
       </c>
-      <c r="F134" s="3" t="inlineStr">
+      <c r="F143" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION lets a 'Central' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G134" s="3" t="inlineStr">
+      <c r="G143" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -9902,57 +10568,57 @@
 23. Q21 = xxxxx</t>
         </is>
       </c>
-      <c r="H134" s="3" t="inlineStr">
+      <c r="H143" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “Central”, then submit.</t>
         </is>
       </c>
-      <c r="I134" s="3" t="inlineStr">
+      <c r="I143" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J134" s="2" t="inlineStr">
+      <c r="J143" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K134" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="n">
-        <v>134</v>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C135" s="3" t="inlineStr">
+      <c r="C144" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>TC-8b99564b2b</t>
         </is>
       </c>
-      <c r="F135" s="3" t="inlineStr">
+      <c r="F144" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION turns a 'North' respondent away once that group has reached its target of 240</t>
         </is>
       </c>
-      <c r="G135" s="3" t="inlineStr">
+      <c r="G144" s="3" t="inlineStr">
         <is>
           <t>FIRST send 240 respondents who answer 'North' at this question, so the group reaches its target. THEN, as respondent number 241:
 1. S1 = Yes
@@ -9980,57 +10646,57 @@
 23. Q21 = xxxxx</t>
         </is>
       </c>
-      <c r="H135" s="3" t="inlineStr">
+      <c r="H144" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “North”, then submit.</t>
         </is>
       </c>
-      <c r="I135" s="3" t="inlineStr">
+      <c r="I144" s="3" t="inlineStr">
         <is>
           <t>1. none of the main-section questions appear at all</t>
         </is>
       </c>
-      <c r="J135" s="2" t="inlineStr">
+      <c r="J144" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K135" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="n">
-        <v>135</v>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C136" s="3" t="inlineStr">
+      <c r="C145" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>TC-a6aba76221</t>
         </is>
       </c>
-      <c r="F136" s="3" t="inlineStr">
+      <c r="F145" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION turns a 'South' respondent away once that group has reached its target of 240</t>
         </is>
       </c>
-      <c r="G136" s="3" t="inlineStr">
+      <c r="G145" s="3" t="inlineStr">
         <is>
           <t>FIRST send 240 respondents who answer 'South' at this question, so the group reaches its target. THEN, as respondent number 241:
 1. S1 = Yes
@@ -10058,57 +10724,57 @@
 23. Q21 = xxxxx</t>
         </is>
       </c>
-      <c r="H136" s="3" t="inlineStr">
+      <c r="H145" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “South”, then submit.</t>
         </is>
       </c>
-      <c r="I136" s="3" t="inlineStr">
+      <c r="I145" s="3" t="inlineStr">
         <is>
           <t>1. none of the main-section questions appear at all</t>
         </is>
       </c>
-      <c r="J136" s="2" t="inlineStr">
+      <c r="J145" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K136" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="n">
-        <v>136</v>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C137" s="3" t="inlineStr">
+      <c r="C146" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>TC-330ea6f3ee</t>
         </is>
       </c>
-      <c r="F137" s="3" t="inlineStr">
+      <c r="F146" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION turns a 'East' respondent away once that group has reached its target of 240</t>
         </is>
       </c>
-      <c r="G137" s="3" t="inlineStr">
+      <c r="G146" s="3" t="inlineStr">
         <is>
           <t>FIRST send 240 respondents who answer 'East' at this question, so the group reaches its target. THEN, as respondent number 241:
 1. S1 = Yes
@@ -10136,57 +10802,57 @@
 23. Q21 = xxxxx</t>
         </is>
       </c>
-      <c r="H137" s="3" t="inlineStr">
+      <c r="H146" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “East”, then submit.</t>
         </is>
       </c>
-      <c r="I137" s="3" t="inlineStr">
+      <c r="I146" s="3" t="inlineStr">
         <is>
           <t>1. none of the main-section questions appear at all</t>
         </is>
       </c>
-      <c r="J137" s="2" t="inlineStr">
+      <c r="J146" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K137" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="n">
-        <v>137</v>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C138" s="3" t="inlineStr">
+      <c r="C147" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>TC-911eec50ce</t>
         </is>
       </c>
-      <c r="F138" s="3" t="inlineStr">
+      <c r="F147" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION turns a 'West' respondent away once that group has reached its target of 240</t>
         </is>
       </c>
-      <c r="G138" s="3" t="inlineStr">
+      <c r="G147" s="3" t="inlineStr">
         <is>
           <t>FIRST send 240 respondents who answer 'West' at this question, so the group reaches its target. THEN, as respondent number 241:
 1. S1 = Yes
@@ -10214,57 +10880,57 @@
 23. Q21 = xxxxx</t>
         </is>
       </c>
-      <c r="H138" s="3" t="inlineStr">
+      <c r="H147" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “West”, then submit.</t>
         </is>
       </c>
-      <c r="I138" s="3" t="inlineStr">
+      <c r="I147" s="3" t="inlineStr">
         <is>
           <t>1. none of the main-section questions appear at all</t>
         </is>
       </c>
-      <c r="J138" s="2" t="inlineStr">
+      <c r="J147" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K138" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="n">
-        <v>138</v>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C139" s="3" t="inlineStr">
+      <c r="C148" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>TC-0e93f23445</t>
         </is>
       </c>
-      <c r="F139" s="3" t="inlineStr">
+      <c r="F148" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION turns a 'Central' respondent away once that group has reached its target of 240</t>
         </is>
       </c>
-      <c r="G139" s="3" t="inlineStr">
+      <c r="G148" s="3" t="inlineStr">
         <is>
           <t>FIRST send 240 respondents who answer 'Central' at this question, so the group reaches its target. THEN, as respondent number 241:
 1. S1 = Yes
@@ -10292,57 +10958,57 @@
 23. Q21 = xxxxx</t>
         </is>
       </c>
-      <c r="H139" s="3" t="inlineStr">
+      <c r="H148" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “Central”, then submit.</t>
         </is>
       </c>
-      <c r="I139" s="3" t="inlineStr">
+      <c r="I148" s="3" t="inlineStr">
         <is>
           <t>1. none of the main-section questions appear at all</t>
         </is>
       </c>
-      <c r="J139" s="2" t="inlineStr">
+      <c r="J148" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K139" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="n">
-        <v>139</v>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C140" s="3" t="inlineStr">
+      <c r="C149" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>TC-c1fe1c973d</t>
         </is>
       </c>
-      <c r="F140" s="3" t="inlineStr">
+      <c r="F149" s="3" t="inlineStr">
         <is>
           <t>Prove the routing sends the respondent to TERM_QUOTA_FULL: when , checked at None. They should then see “”.</t>
         </is>
       </c>
-      <c r="G140" s="3" t="inlineStr">
+      <c r="G149" s="3" t="inlineStr">
         <is>
           <t>FIRST send 240 respondents who answer 'North' at this question, so the group reaches its target. THEN, as respondent number 241:
 1. S1 = Yes
@@ -10371,57 +11037,447 @@
 24. D1 = North</t>
         </is>
       </c>
-      <c r="H140" s="3" t="inlineStr">
+      <c r="H149" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I140" s="3" t="inlineStr">
+      <c r="I149" s="3" t="inlineStr">
         <is>
           <t>1. none of the main-section questions appear at all</t>
         </is>
       </c>
-      <c r="J140" s="2" t="inlineStr">
+      <c r="J149" s="2" t="inlineStr">
         <is>
           <t>Survey ends in the right place</t>
         </is>
       </c>
-      <c r="K140" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="n">
-        <v>140</v>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>TC-39e506e5ad</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>Prove quota QUOTA_REGION turns a 'North' respondent away once that group has reached its target of 240</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>FIRST send 1 respondents who answer 'South' at this question, so the group reaches its target. THEN, as respondent number 2:
+1. S1 = Yes
+2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
+3. S3 = No
+4. S4 = No
+5. Q1 = Auto Brand A
+6. Q2 = Auto Brand A
+7. Q3 = Auto Brand A
+8. Q4 = Initial research
+9. Q5 = Manufacturer website
+10. Q6 = Manufacturer website
+11. Q7 = Very poor
+12. Q8 = 0
+13. Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor...
+14. Q10 = Yes
+15. Q11 = Phone
+16. Q12 = Fully
+17. Q13 = Very low
+18. Q15 = Yes
+19. Q16 = Price
+20. Q18 = Price=20; Quality=20; Convenience=20...
+21. Q19 = Concept A
+22. Q20 = Very poor
+23. Q21 = xxxxx</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>At D1, choose “South”, then submit.</t>
+        </is>
+      </c>
+      <c r="I150" s="3" t="inlineStr">
+        <is>
+          <t>1. quota counter unchanged</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>Quota accepts or turns away</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>TC-2f2ca06f01</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>Prove quota QUOTA_REGION turns a 'South' respondent away once that group has reached its target of 240</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>FIRST send 1 respondents who answer 'North' at this question, so the group reaches its target. THEN, as respondent number 2:
+1. S1 = Yes
+2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
+3. S3 = No
+4. S4 = No
+5. Q1 = Auto Brand A
+6. Q2 = Auto Brand A
+7. Q3 = Auto Brand A
+8. Q4 = Initial research
+9. Q5 = Manufacturer website
+10. Q6 = Manufacturer website
+11. Q7 = Very poor
+12. Q8 = 0
+13. Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor...
+14. Q10 = Yes
+15. Q11 = Phone
+16. Q12 = Fully
+17. Q13 = Very low
+18. Q15 = Yes
+19. Q16 = Price
+20. Q18 = Price=20; Quality=20; Convenience=20...
+21. Q19 = Concept A
+22. Q20 = Very poor
+23. Q21 = xxxxx</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>At D1, choose “North”, then submit.</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>1. quota counter unchanged</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>Quota accepts or turns away</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>TC-f1869aa04b</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>Prove quota QUOTA_REGION turns a 'East' respondent away once that group has reached its target of 240  [Same actions as TC-2f2ca06f01 on this question: the questionnaire's answer rule and its compulsory setting come down to the same thing here. Both are kept because they are separate claims, but one run satisfies both.]</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>FIRST send 1 respondents who answer 'North' at this question, so the group reaches its target. THEN, as respondent number 2:
+1. S1 = Yes
+2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
+3. S3 = No
+4. S4 = No
+5. Q1 = Auto Brand A
+6. Q2 = Auto Brand A
+7. Q3 = Auto Brand A
+8. Q4 = Initial research
+9. Q5 = Manufacturer website
+10. Q6 = Manufacturer website
+11. Q7 = Very poor
+12. Q8 = 0
+13. Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor...
+14. Q10 = Yes
+15. Q11 = Phone
+16. Q12 = Fully
+17. Q13 = Very low
+18. Q15 = Yes
+19. Q16 = Price
+20. Q18 = Price=20; Quality=20; Convenience=20...
+21. Q19 = Concept A
+22. Q20 = Very poor
+23. Q21 = xxxxx</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>At D1, choose “North”, then submit.</t>
+        </is>
+      </c>
+      <c r="I152" s="3" t="inlineStr">
+        <is>
+          <t>1. quota counter unchanged</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>Quota accepts or turns away</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>TC-595208d8f1</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>Prove quota QUOTA_REGION turns a 'West' respondent away once that group has reached its target of 240  [Same actions as TC-2f2ca06f01 on this question: the questionnaire's answer rule and its compulsory setting come down to the same thing here. Both are kept because they are separate claims, but one run satisfies both.]</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>FIRST send 1 respondents who answer 'North' at this question, so the group reaches its target. THEN, as respondent number 2:
+1. S1 = Yes
+2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
+3. S3 = No
+4. S4 = No
+5. Q1 = Auto Brand A
+6. Q2 = Auto Brand A
+7. Q3 = Auto Brand A
+8. Q4 = Initial research
+9. Q5 = Manufacturer website
+10. Q6 = Manufacturer website
+11. Q7 = Very poor
+12. Q8 = 0
+13. Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor...
+14. Q10 = Yes
+15. Q11 = Phone
+16. Q12 = Fully
+17. Q13 = Very low
+18. Q15 = Yes
+19. Q16 = Price
+20. Q18 = Price=20; Quality=20; Convenience=20...
+21. Q19 = Concept A
+22. Q20 = Very poor
+23. Q21 = xxxxx</t>
+        </is>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>At D1, choose “North”, then submit.</t>
+        </is>
+      </c>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t>1. quota counter unchanged</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>Quota accepts or turns away</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>TC-7e8559f867</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>Prove quota QUOTA_REGION turns a 'Central' respondent away once that group has reached its target of 240  [Same actions as TC-2f2ca06f01 on this question: the questionnaire's answer rule and its compulsory setting come down to the same thing here. Both are kept because they are separate claims, but one run satisfies both.]</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>FIRST send 1 respondents who answer 'North' at this question, so the group reaches its target. THEN, as respondent number 2:
+1. S1 = Yes
+2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
+3. S3 = No
+4. S4 = No
+5. Q1 = Auto Brand A
+6. Q2 = Auto Brand A
+7. Q3 = Auto Brand A
+8. Q4 = Initial research
+9. Q5 = Manufacturer website
+10. Q6 = Manufacturer website
+11. Q7 = Very poor
+12. Q8 = 0
+13. Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor...
+14. Q10 = Yes
+15. Q11 = Phone
+16. Q12 = Fully
+17. Q13 = Very low
+18. Q15 = Yes
+19. Q16 = Price
+20. Q18 = Price=20; Quality=20; Convenience=20...
+21. Q19 = Concept A
+22. Q20 = Very poor
+23. Q21 = xxxxx</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>At D1, choose “North”, then submit.</t>
+        </is>
+      </c>
+      <c r="I154" s="3" t="inlineStr">
+        <is>
+          <t>1. quota counter unchanged</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>Quota accepts or turns away</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C141" s="3" t="inlineStr">
+      <c r="C155" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
         </is>
       </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>TC-a1ac064e4d</t>
         </is>
       </c>
-      <c r="F141" s="3" t="inlineStr">
+      <c r="F155" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at D2: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G141" s="3" t="inlineStr">
+      <c r="G155" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -10453,58 +11509,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H141" s="3" t="inlineStr">
+      <c r="H155" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I141" s="3" t="inlineStr">
+      <c r="I155" s="3" t="inlineStr">
         <is>
           <t>1. D2 IS shown on the page
 2. the next question shown is D3</t>
         </is>
       </c>
-      <c r="J141" s="2" t="inlineStr">
+      <c r="J155" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K141" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="n">
-        <v>141</v>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C142" s="3" t="inlineStr">
+      <c r="C156" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>TC-e3d95ddd0a</t>
         </is>
       </c>
-      <c r="F142" s="3" t="inlineStr">
+      <c r="F156" s="3" t="inlineStr">
         <is>
           <t>Prove D2 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G142" s="3" t="inlineStr">
+      <c r="G156" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -10532,58 +11588,58 @@
 24. D1 = North</t>
         </is>
       </c>
-      <c r="H142" s="3" t="inlineStr">
+      <c r="H156" s="3" t="inlineStr">
         <is>
           <t>At D2, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I142" s="3" t="inlineStr">
+      <c r="I156" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against D2</t>
         </is>
       </c>
-      <c r="J142" s="2" t="inlineStr">
+      <c r="J156" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K142" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="n">
-        <v>142</v>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C143" s="3" t="inlineStr">
+      <c r="C157" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
         </is>
       </c>
-      <c r="D143" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>TC-9e12b71968</t>
         </is>
       </c>
-      <c r="F143" s="3" t="inlineStr">
+      <c r="F157" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_AGE lets a '21-29' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G143" s="3" t="inlineStr">
+      <c r="G157" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -10611,57 +11667,57 @@
 24. D1 = North</t>
         </is>
       </c>
-      <c r="H143" s="3" t="inlineStr">
+      <c r="H157" s="3" t="inlineStr">
         <is>
           <t>At D2, choose “21-29”, then submit.</t>
         </is>
       </c>
-      <c r="I143" s="3" t="inlineStr">
+      <c r="I157" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J143" s="2" t="inlineStr">
+      <c r="J157" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K143" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="n">
-        <v>143</v>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C144" s="3" t="inlineStr">
+      <c r="C158" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>TC-6c5662fab4</t>
         </is>
       </c>
-      <c r="F144" s="3" t="inlineStr">
+      <c r="F158" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_AGE lets a '30-39' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G144" s="3" t="inlineStr">
+      <c r="G158" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -10689,57 +11745,57 @@
 24. D1 = North</t>
         </is>
       </c>
-      <c r="H144" s="3" t="inlineStr">
+      <c r="H158" s="3" t="inlineStr">
         <is>
           <t>At D2, choose “30-39”, then submit.</t>
         </is>
       </c>
-      <c r="I144" s="3" t="inlineStr">
+      <c r="I158" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J144" s="2" t="inlineStr">
+      <c r="J158" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K144" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="n">
-        <v>144</v>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C145" s="3" t="inlineStr">
+      <c r="C159" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>TC-dd41da385a</t>
         </is>
       </c>
-      <c r="F145" s="3" t="inlineStr">
+      <c r="F159" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_AGE lets a '40-49' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G145" s="3" t="inlineStr">
+      <c r="G159" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -10767,57 +11823,57 @@
 24. D1 = North</t>
         </is>
       </c>
-      <c r="H145" s="3" t="inlineStr">
+      <c r="H159" s="3" t="inlineStr">
         <is>
           <t>At D2, choose “40-49”, then submit.</t>
         </is>
       </c>
-      <c r="I145" s="3" t="inlineStr">
+      <c r="I159" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J145" s="2" t="inlineStr">
+      <c r="J159" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K145" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="n">
-        <v>145</v>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C146" s="3" t="inlineStr">
+      <c r="C160" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>TC-d79d3aefa5</t>
         </is>
       </c>
-      <c r="F146" s="3" t="inlineStr">
+      <c r="F160" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_AGE lets a '50-59' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G146" s="3" t="inlineStr">
+      <c r="G160" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -10845,57 +11901,57 @@
 24. D1 = North</t>
         </is>
       </c>
-      <c r="H146" s="3" t="inlineStr">
+      <c r="H160" s="3" t="inlineStr">
         <is>
           <t>At D2, choose “50-59”, then submit.</t>
         </is>
       </c>
-      <c r="I146" s="3" t="inlineStr">
+      <c r="I160" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J146" s="2" t="inlineStr">
+      <c r="J160" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K146" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="n">
-        <v>146</v>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C147" s="3" t="inlineStr">
+      <c r="C161" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
         </is>
       </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>TC-718cbe9fd7</t>
         </is>
       </c>
-      <c r="F147" s="3" t="inlineStr">
+      <c r="F161" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_AGE lets a '60+' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G147" s="3" t="inlineStr">
+      <c r="G161" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -10923,57 +11979,57 @@
 24. D1 = North</t>
         </is>
       </c>
-      <c r="H147" s="3" t="inlineStr">
+      <c r="H161" s="3" t="inlineStr">
         <is>
           <t>At D2, choose “60+”, then submit.</t>
         </is>
       </c>
-      <c r="I147" s="3" t="inlineStr">
+      <c r="I161" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J147" s="2" t="inlineStr">
+      <c r="J161" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K147" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="n">
-        <v>147</v>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C148" s="3" t="inlineStr">
+      <c r="C162" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr">
-        <is>
-          <t>TC-dd97cdad02</t>
-        </is>
-      </c>
-      <c r="F148" s="3" t="inlineStr">
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>TC-6a0503ad62</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_AGE turns a '21-29' respondent away once that group has reached its target of 240</t>
         </is>
       </c>
-      <c r="G148" s="3" t="inlineStr">
+      <c r="G162" s="3" t="inlineStr">
         <is>
           <t>FIRST send 240 respondents who answer '21-29' at this question, so the group reaches its target. THEN, as respondent number 241:
 1. S1 = Yes
@@ -11002,59 +12058,60 @@
 24. D1 = North</t>
         </is>
       </c>
-      <c r="H148" s="3" t="inlineStr">
+      <c r="H162" s="3" t="inlineStr">
         <is>
           <t>At D2, choose “21-29”, then submit.</t>
         </is>
       </c>
-      <c r="I148" s="3" t="inlineStr">
-        <is>
-          <t>1. none of the main-section questions appear at all</t>
-        </is>
-      </c>
-      <c r="J148" s="2" t="inlineStr">
+      <c r="I162" s="3" t="inlineStr">
+        <is>
+          <t>1. the respondent is allowed to continue, not sent to the quota-full ending
+2. quota counter over target</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K148" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="n">
-        <v>148</v>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C149" s="3" t="inlineStr">
+      <c r="C163" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
         </is>
       </c>
-      <c r="D149" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr">
-        <is>
-          <t>TC-99a0166154</t>
-        </is>
-      </c>
-      <c r="F149" s="3" t="inlineStr">
-        <is>
-          <t>Prove quota QUOTA_AGE turns a '30-39' respondent away once that group has reached its target of 300</t>
-        </is>
-      </c>
-      <c r="G149" s="3" t="inlineStr">
-        <is>
-          <t>FIRST send 300 respondents who answer '30-39' at this question, so the group reaches its target. THEN, as respondent number 301:
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>TC-3d418eda45</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>Prove quota QUOTA_AGE turns a '21-29' respondent away once that group has reached its target of 240</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t>FIRST send 1 respondents who answer '30-39' at this question, so the group reaches its target. THEN, as respondent number 2:
 1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
 3. S3 = No
@@ -11081,59 +12138,59 @@
 24. D1 = North</t>
         </is>
       </c>
-      <c r="H149" s="3" t="inlineStr">
+      <c r="H163" s="3" t="inlineStr">
         <is>
           <t>At D2, choose “30-39”, then submit.</t>
         </is>
       </c>
-      <c r="I149" s="3" t="inlineStr">
-        <is>
-          <t>1. none of the main-section questions appear at all</t>
-        </is>
-      </c>
-      <c r="J149" s="2" t="inlineStr">
+      <c r="I163" s="3" t="inlineStr">
+        <is>
+          <t>1. quota counter unchanged</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K149" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="n">
-        <v>149</v>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C150" s="3" t="inlineStr">
+      <c r="C164" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
         </is>
       </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>TC-7a14a8b4e6</t>
-        </is>
-      </c>
-      <c r="F150" s="3" t="inlineStr">
-        <is>
-          <t>Prove quota QUOTA_AGE turns a '40-49' respondent away once that group has reached its target of 300</t>
-        </is>
-      </c>
-      <c r="G150" s="3" t="inlineStr">
-        <is>
-          <t>FIRST send 300 respondents who answer '40-49' at this question, so the group reaches its target. THEN, as respondent number 301:
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>TC-00f21cb983</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>Prove quota QUOTA_AGE turns a '30-39' respondent away once that group has reached its target of 300</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>FIRST send 300 respondents who answer '30-39' at this question, so the group reaches its target. THEN, as respondent number 301:
 1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
 3. S3 = No
@@ -11160,59 +12217,60 @@
 24. D1 = North</t>
         </is>
       </c>
-      <c r="H150" s="3" t="inlineStr">
-        <is>
-          <t>At D2, choose “40-49”, then submit.</t>
-        </is>
-      </c>
-      <c r="I150" s="3" t="inlineStr">
-        <is>
-          <t>1. none of the main-section questions appear at all</t>
-        </is>
-      </c>
-      <c r="J150" s="2" t="inlineStr">
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>At D2, choose “30-39”, then submit.</t>
+        </is>
+      </c>
+      <c r="I164" s="3" t="inlineStr">
+        <is>
+          <t>1. the respondent is allowed to continue, not sent to the quota-full ending
+2. quota counter over target</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K150" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C151" s="3" t="inlineStr">
+      <c r="C165" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
         </is>
       </c>
-      <c r="D151" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E151" s="2" t="inlineStr">
-        <is>
-          <t>TC-de18dce408</t>
-        </is>
-      </c>
-      <c r="F151" s="3" t="inlineStr">
-        <is>
-          <t>Prove quota QUOTA_AGE turns a '50-59' respondent away once that group has reached its target of 240</t>
-        </is>
-      </c>
-      <c r="G151" s="3" t="inlineStr">
-        <is>
-          <t>FIRST send 240 respondents who answer '50-59' at this question, so the group reaches its target. THEN, as respondent number 241:
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>TC-e89e93f8c4</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>Prove quota QUOTA_AGE turns a '30-39' respondent away once that group has reached its target of 300</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="inlineStr">
+        <is>
+          <t>FIRST send 1 respondents who answer '21-29' at this question, so the group reaches its target. THEN, as respondent number 2:
 1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
 3. S3 = No
@@ -11239,59 +12297,59 @@
 24. D1 = North</t>
         </is>
       </c>
-      <c r="H151" s="3" t="inlineStr">
-        <is>
-          <t>At D2, choose “50-59”, then submit.</t>
-        </is>
-      </c>
-      <c r="I151" s="3" t="inlineStr">
-        <is>
-          <t>1. none of the main-section questions appear at all</t>
-        </is>
-      </c>
-      <c r="J151" s="2" t="inlineStr">
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>At D2, choose “21-29”, then submit.</t>
+        </is>
+      </c>
+      <c r="I165" s="3" t="inlineStr">
+        <is>
+          <t>1. quota counter unchanged</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K151" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="n">
-        <v>151</v>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C152" s="3" t="inlineStr">
+      <c r="C166" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>TC-196b139f41</t>
-        </is>
-      </c>
-      <c r="F152" s="3" t="inlineStr">
-        <is>
-          <t>Prove quota QUOTA_AGE turns a '60+' respondent away once that group has reached its target of 120</t>
-        </is>
-      </c>
-      <c r="G152" s="3" t="inlineStr">
-        <is>
-          <t>FIRST send 120 respondents who answer '60+' at this question, so the group reaches its target. THEN, as respondent number 121:
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>TC-a8af66937a</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>Prove quota QUOTA_AGE turns a '40-49' respondent away once that group has reached its target of 300</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t>FIRST send 300 respondents who answer '40-49' at this question, so the group reaches its target. THEN, as respondent number 301:
 1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
 3. S3 = No
@@ -11318,57 +12376,455 @@
 24. D1 = North</t>
         </is>
       </c>
-      <c r="H152" s="3" t="inlineStr">
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>At D2, choose “40-49”, then submit.</t>
+        </is>
+      </c>
+      <c r="I166" s="3" t="inlineStr">
+        <is>
+          <t>1. the respondent is allowed to continue, not sent to the quota-full ending
+2. quota counter over target</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>Quota accepts or turns away</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>TC-f29e54ea44</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>Prove quota QUOTA_AGE turns a '40-49' respondent away once that group has reached its target of 300  [Same actions as TC-e89e93f8c4 on this question: the questionnaire's answer rule and its compulsory setting come down to the same thing here. Both are kept because they are separate claims, but one run satisfies both.]</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="inlineStr">
+        <is>
+          <t>FIRST send 1 respondents who answer '21-29' at this question, so the group reaches its target. THEN, as respondent number 2:
+1. S1 = Yes
+2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
+3. S3 = No
+4. S4 = No
+5. Q1 = Auto Brand A
+6. Q2 = Auto Brand A
+7. Q3 = Auto Brand A
+8. Q4 = Initial research
+9. Q5 = Manufacturer website
+10. Q6 = Manufacturer website
+11. Q7 = Very poor
+12. Q8 = 0
+13. Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor...
+14. Q10 = Yes
+15. Q11 = Phone
+16. Q12 = Fully
+17. Q13 = Very low
+18. Q15 = Yes
+19. Q16 = Price
+20. Q18 = Price=20; Quality=20; Convenience=20...
+21. Q19 = Concept A
+22. Q20 = Very poor
+23. Q21 = xxxxx
+24. D1 = North</t>
+        </is>
+      </c>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>At D2, choose “21-29”, then submit.</t>
+        </is>
+      </c>
+      <c r="I167" s="3" t="inlineStr">
+        <is>
+          <t>1. quota counter unchanged</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>Quota accepts or turns away</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>TC-9e8ae8681c</t>
+        </is>
+      </c>
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>Prove quota QUOTA_AGE turns a '50-59' respondent away once that group has reached its target of 240</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="inlineStr">
+        <is>
+          <t>FIRST send 240 respondents who answer '50-59' at this question, so the group reaches its target. THEN, as respondent number 241:
+1. S1 = Yes
+2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
+3. S3 = No
+4. S4 = No
+5. Q1 = Auto Brand A
+6. Q2 = Auto Brand A
+7. Q3 = Auto Brand A
+8. Q4 = Initial research
+9. Q5 = Manufacturer website
+10. Q6 = Manufacturer website
+11. Q7 = Very poor
+12. Q8 = 0
+13. Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor...
+14. Q10 = Yes
+15. Q11 = Phone
+16. Q12 = Fully
+17. Q13 = Very low
+18. Q15 = Yes
+19. Q16 = Price
+20. Q18 = Price=20; Quality=20; Convenience=20...
+21. Q19 = Concept A
+22. Q20 = Very poor
+23. Q21 = xxxxx
+24. D1 = North</t>
+        </is>
+      </c>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>At D2, choose “50-59”, then submit.</t>
+        </is>
+      </c>
+      <c r="I168" s="3" t="inlineStr">
+        <is>
+          <t>1. the respondent is allowed to continue, not sent to the quota-full ending
+2. quota counter over target</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>Quota accepts or turns away</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>TC-46f19ace6d</t>
+        </is>
+      </c>
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>Prove quota QUOTA_AGE turns a '50-59' respondent away once that group has reached its target of 240  [Same actions as TC-e89e93f8c4 on this question: the questionnaire's answer rule and its compulsory setting come down to the same thing here. Both are kept because they are separate claims, but one run satisfies both.]</t>
+        </is>
+      </c>
+      <c r="G169" s="3" t="inlineStr">
+        <is>
+          <t>FIRST send 1 respondents who answer '21-29' at this question, so the group reaches its target. THEN, as respondent number 2:
+1. S1 = Yes
+2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
+3. S3 = No
+4. S4 = No
+5. Q1 = Auto Brand A
+6. Q2 = Auto Brand A
+7. Q3 = Auto Brand A
+8. Q4 = Initial research
+9. Q5 = Manufacturer website
+10. Q6 = Manufacturer website
+11. Q7 = Very poor
+12. Q8 = 0
+13. Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor...
+14. Q10 = Yes
+15. Q11 = Phone
+16. Q12 = Fully
+17. Q13 = Very low
+18. Q15 = Yes
+19. Q16 = Price
+20. Q18 = Price=20; Quality=20; Convenience=20...
+21. Q19 = Concept A
+22. Q20 = Very poor
+23. Q21 = xxxxx
+24. D1 = North</t>
+        </is>
+      </c>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>At D2, choose “21-29”, then submit.</t>
+        </is>
+      </c>
+      <c r="I169" s="3" t="inlineStr">
+        <is>
+          <t>1. quota counter unchanged</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>Quota accepts or turns away</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>TC-8323b8ca60</t>
+        </is>
+      </c>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t>Prove quota QUOTA_AGE turns a '60+' respondent away once that group has reached its target of 120</t>
+        </is>
+      </c>
+      <c r="G170" s="3" t="inlineStr">
+        <is>
+          <t>FIRST send 120 respondents who answer '60+' at this question, so the group reaches its target. THEN, as respondent number 121:
+1. S1 = Yes
+2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
+3. S3 = No
+4. S4 = No
+5. Q1 = Auto Brand A
+6. Q2 = Auto Brand A
+7. Q3 = Auto Brand A
+8. Q4 = Initial research
+9. Q5 = Manufacturer website
+10. Q6 = Manufacturer website
+11. Q7 = Very poor
+12. Q8 = 0
+13. Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor...
+14. Q10 = Yes
+15. Q11 = Phone
+16. Q12 = Fully
+17. Q13 = Very low
+18. Q15 = Yes
+19. Q16 = Price
+20. Q18 = Price=20; Quality=20; Convenience=20...
+21. Q19 = Concept A
+22. Q20 = Very poor
+23. Q21 = xxxxx
+24. D1 = North</t>
+        </is>
+      </c>
+      <c r="H170" s="3" t="inlineStr">
         <is>
           <t>At D2, choose “60+”, then submit.</t>
         </is>
       </c>
-      <c r="I152" s="3" t="inlineStr">
-        <is>
-          <t>1. none of the main-section questions appear at all</t>
-        </is>
-      </c>
-      <c r="J152" s="2" t="inlineStr">
+      <c r="I170" s="3" t="inlineStr">
+        <is>
+          <t>1. the respondent is allowed to continue, not sent to the quota-full ending
+2. quota counter over target</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K152" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="n">
-        <v>152</v>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>TC-480eae6349</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>Prove quota QUOTA_AGE turns a '60+' respondent away once that group has reached its target of 120  [Same actions as TC-e89e93f8c4 on this question: the questionnaire's answer rule and its compulsory setting come down to the same thing here. Both are kept because they are separate claims, but one run satisfies both.]</t>
+        </is>
+      </c>
+      <c r="G171" s="3" t="inlineStr">
+        <is>
+          <t>FIRST send 1 respondents who answer '21-29' at this question, so the group reaches its target. THEN, as respondent number 2:
+1. S1 = Yes
+2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
+3. S3 = No
+4. S4 = No
+5. Q1 = Auto Brand A
+6. Q2 = Auto Brand A
+7. Q3 = Auto Brand A
+8. Q4 = Initial research
+9. Q5 = Manufacturer website
+10. Q6 = Manufacturer website
+11. Q7 = Very poor
+12. Q8 = 0
+13. Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor...
+14. Q10 = Yes
+15. Q11 = Phone
+16. Q12 = Fully
+17. Q13 = Very low
+18. Q15 = Yes
+19. Q16 = Price
+20. Q18 = Price=20; Quality=20; Convenience=20...
+21. Q19 = Concept A
+22. Q20 = Very poor
+23. Q21 = xxxxx
+24. D1 = North</t>
+        </is>
+      </c>
+      <c r="H171" s="3" t="inlineStr">
+        <is>
+          <t>At D2, choose “21-29”, then submit.</t>
+        </is>
+      </c>
+      <c r="I171" s="3" t="inlineStr">
+        <is>
+          <t>1. quota counter unchanged</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>Quota accepts or turns away</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="C153" s="3" t="inlineStr">
+      <c r="C172" s="3" t="inlineStr">
         <is>
           <t>D3 | How do you describe your gender? | single | Woman; Man; Non-binary; Prefer to self-describe; Prefer not to say | Always show</t>
         </is>
       </c>
-      <c r="D153" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>TC-531a6544ed</t>
         </is>
       </c>
-      <c r="F153" s="3" t="inlineStr">
+      <c r="F172" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at D3: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G153" s="3" t="inlineStr">
+      <c r="G172" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -11400,58 +12856,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H153" s="3" t="inlineStr">
+      <c r="H172" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I153" s="3" t="inlineStr">
+      <c r="I172" s="3" t="inlineStr">
         <is>
           <t>1. D3 IS shown on the page
 2. the next question shown is D4</t>
         </is>
       </c>
-      <c r="J153" s="2" t="inlineStr">
+      <c r="J172" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K153" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="n">
-        <v>153</v>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="C154" s="3" t="inlineStr">
+      <c r="C173" s="3" t="inlineStr">
         <is>
           <t>D3 | How do you describe your gender? | single | Woman; Man; Non-binary; Prefer to self-describe; Prefer not to say | Always show</t>
         </is>
       </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>TC-799f9fd202</t>
         </is>
       </c>
-      <c r="F154" s="3" t="inlineStr">
+      <c r="F173" s="3" t="inlineStr">
         <is>
           <t>Prove D3 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G154" s="3" t="inlineStr">
+      <c r="G173" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -11480,58 +12936,58 @@
 25. D2 = 21-29</t>
         </is>
       </c>
-      <c r="H154" s="3" t="inlineStr">
+      <c r="H173" s="3" t="inlineStr">
         <is>
           <t>At D3, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I154" s="3" t="inlineStr">
+      <c r="I173" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against D3</t>
         </is>
       </c>
-      <c r="J154" s="2" t="inlineStr">
+      <c r="J173" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K154" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="n">
-        <v>154</v>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="C155" s="3" t="inlineStr">
+      <c r="C174" s="3" t="inlineStr">
         <is>
           <t>D4 | What is your household or organizational decision band? | single | Band 1; Band 2; Band 3; Band 4; Prefer not to say | Always show</t>
         </is>
       </c>
-      <c r="D155" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>TC-0c2ebe3557</t>
         </is>
       </c>
-      <c r="F155" s="3" t="inlineStr">
+      <c r="F174" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at D4: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G155" s="3" t="inlineStr">
+      <c r="G174" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -11563,58 +13019,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H155" s="3" t="inlineStr">
+      <c r="H174" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I155" s="3" t="inlineStr">
+      <c r="I174" s="3" t="inlineStr">
         <is>
           <t>1. D4 IS shown on the page
 2. the next question shown is Q22</t>
         </is>
       </c>
-      <c r="J155" s="2" t="inlineStr">
+      <c r="J174" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K155" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="n">
-        <v>155</v>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="C156" s="3" t="inlineStr">
+      <c r="C175" s="3" t="inlineStr">
         <is>
           <t>D4 | What is your household or organizational decision band? | single | Band 1; Band 2; Band 3; Band 4; Prefer not to say | Always show</t>
         </is>
       </c>
-      <c r="D156" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>TC-6408b44286</t>
         </is>
       </c>
-      <c r="F156" s="3" t="inlineStr">
+      <c r="F175" s="3" t="inlineStr">
         <is>
           <t>Prove D4 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G156" s="3" t="inlineStr">
+      <c r="G175" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -11644,58 +13100,58 @@
 26. D3 = Woman</t>
         </is>
       </c>
-      <c r="H156" s="3" t="inlineStr">
+      <c r="H175" s="3" t="inlineStr">
         <is>
           <t>At D4, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I156" s="3" t="inlineStr">
+      <c r="I175" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against D4</t>
         </is>
       </c>
-      <c r="J156" s="2" t="inlineStr">
+      <c r="J175" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K156" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="n">
-        <v>156</v>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>Q22</t>
         </is>
       </c>
-      <c r="C157" s="3" t="inlineStr">
+      <c r="C176" s="3" t="inlineStr">
         <is>
           <t>Q22 | May we use your anonymized comments in internal reporting? | single | Yes; No | Always show</t>
         </is>
       </c>
-      <c r="D157" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>TC-d3a3106833</t>
         </is>
       </c>
-      <c r="F157" s="3" t="inlineStr">
+      <c r="F176" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q22: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G157" s="3" t="inlineStr">
+      <c r="G176" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -11727,58 +13183,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H157" s="3" t="inlineStr">
+      <c r="H176" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I157" s="3" t="inlineStr">
+      <c r="I176" s="3" t="inlineStr">
         <is>
           <t>1. Q22 IS shown on the page
 2. the next question shown is Q23</t>
         </is>
       </c>
-      <c r="J157" s="2" t="inlineStr">
+      <c r="J176" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K157" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>Q22</t>
         </is>
       </c>
-      <c r="C158" s="3" t="inlineStr">
+      <c r="C177" s="3" t="inlineStr">
         <is>
           <t>Q22 | May we use your anonymized comments in internal reporting? | single | Yes; No | Always show</t>
         </is>
       </c>
-      <c r="D158" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>TC-7596aff04a</t>
         </is>
       </c>
-      <c r="F158" s="3" t="inlineStr">
+      <c r="F177" s="3" t="inlineStr">
         <is>
           <t>Prove Q22 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G158" s="3" t="inlineStr">
+      <c r="G177" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -11809,59 +13265,59 @@
 27. D4 = Band 1</t>
         </is>
       </c>
-      <c r="H158" s="3" t="inlineStr">
+      <c r="H177" s="3" t="inlineStr">
         <is>
           <t>At Q22, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I158" s="3" t="inlineStr">
+      <c r="I177" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q22</t>
         </is>
       </c>
-      <c r="J158" s="2" t="inlineStr">
+      <c r="J177" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K158" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="n">
-        <v>158</v>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>Q23</t>
         </is>
       </c>
-      <c r="C159" s="3" t="inlineStr">
+      <c r="C178" s="3" t="inlineStr">
         <is>
           <t>Q23 | Any final comments? | text | — | Validate: {"max_length": 1000}
 Optional</t>
         </is>
       </c>
-      <c r="D159" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>TC-66de0d40bf</t>
         </is>
       </c>
-      <c r="F159" s="3" t="inlineStr">
+      <c r="F178" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q23: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G159" s="3" t="inlineStr">
+      <c r="G178" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -11893,59 +13349,59 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H159" s="3" t="inlineStr">
+      <c r="H178" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I159" s="3" t="inlineStr">
+      <c r="I178" s="3" t="inlineStr">
         <is>
           <t>1. Q23 IS shown on the page
 2. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
-      <c r="J159" s="2" t="inlineStr">
+      <c r="J178" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K159" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="n">
-        <v>159</v>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>Q23</t>
         </is>
       </c>
-      <c r="C160" s="3" t="inlineStr">
+      <c r="C179" s="3" t="inlineStr">
         <is>
           <t>Q23 | Any final comments? | text | — | Validate: {"max_length": 1000}
 Optional</t>
         </is>
       </c>
-      <c r="D160" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>TC-27239f8502</t>
         </is>
       </c>
-      <c r="F160" s="3" t="inlineStr">
+      <c r="F179" s="3" t="inlineStr">
         <is>
           <t>Prove Q23 ACCEPTS an answer that obeys its rule. The QRE's rule is: the answer must be at most 1000 characters</t>
         </is>
       </c>
-      <c r="G160" s="3" t="inlineStr">
+      <c r="G179" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -11977,58 +13433,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H160" s="3" t="inlineStr">
+      <c r="H179" s="3" t="inlineStr">
         <is>
           <t>At Q23, type “x”, then submit.</t>
         </is>
       </c>
-      <c r="I160" s="3" t="inlineStr">
+      <c r="I179" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J160" s="2" t="inlineStr">
+      <c r="J179" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K160" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="n">
-        <v>160</v>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>Q23</t>
         </is>
       </c>
-      <c r="C161" s="3" t="inlineStr">
+      <c r="C180" s="3" t="inlineStr">
         <is>
           <t>Q23 | Any final comments? | text | — | Validate: {"max_length": 1000}
 Optional</t>
         </is>
       </c>
-      <c r="D161" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>TC-de6bfa278d</t>
         </is>
       </c>
-      <c r="F161" s="3" t="inlineStr">
+      <c r="F180" s="3" t="inlineStr">
         <is>
           <t>Prove Q23 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at most 1000 characters</t>
         </is>
       </c>
-      <c r="G161" s="3" t="inlineStr">
+      <c r="G180" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -12060,59 +13516,59 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H161" s="3" t="inlineStr">
+      <c r="H180" s="3" t="inlineStr">
         <is>
           <t>At Q23, type a 1001-character answer, then submit.</t>
         </is>
       </c>
-      <c r="I161" s="3" t="inlineStr">
+      <c r="I180" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q23</t>
         </is>
       </c>
-      <c r="J161" s="2" t="inlineStr">
+      <c r="J180" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K161" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="n">
-        <v>161</v>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>Q23</t>
         </is>
       </c>
-      <c r="C162" s="3" t="inlineStr">
+      <c r="C181" s="3" t="inlineStr">
         <is>
           <t>Q23 | Any final comments? | text | — | Validate: {"max_length": 1000}
 Optional</t>
         </is>
       </c>
-      <c r="D162" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>TC-501913f6da</t>
         </is>
       </c>
-      <c r="F162" s="3" t="inlineStr">
+      <c r="F181" s="3" t="inlineStr">
         <is>
           <t>Prove Q23 lets the respondent through with no answer, because the questionnaire marks it optional</t>
         </is>
       </c>
-      <c r="G162" s="3" t="inlineStr">
+      <c r="G181" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -12144,53 +13600,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H162" s="3" t="inlineStr">
+      <c r="H181" s="3" t="inlineStr">
         <is>
           <t>At Q23, type nothing, then submit.</t>
         </is>
       </c>
-      <c r="I162" s="3" t="inlineStr">
+      <c r="I181" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J162" s="2" t="inlineStr">
+      <c r="J181" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K162" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="n">
-        <v>162</v>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>whole survey</t>
-        </is>
-      </c>
-      <c r="C163" s="3" t="inlineStr"/>
-      <c r="D163" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E163" s="2" t="inlineStr">
-        <is>
-          <t>TC-236280087d</t>
-        </is>
-      </c>
-      <c r="F163" s="3" t="inlineStr">
-        <is>
-          <t>Prove the survey finishes normally for a respondent who answers everything and triggers no screen-out</t>
-        </is>
-      </c>
-      <c r="G163" s="3" t="inlineStr">
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>Q23</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>Q23 | Any final comments? | text | — | Validate: {"max_length": 1000}
+Optional</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>TC-e8a2b0563a</t>
+        </is>
+      </c>
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q23 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at most 1000 characters</t>
+        </is>
+      </c>
+      <c r="G182" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
@@ -12222,22 +13683,266 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H163" s="3" t="inlineStr">
+      <c r="H182" s="3" t="inlineStr">
+        <is>
+          <t>At Q23, type a 1000-character answer, then submit.</t>
+        </is>
+      </c>
+      <c r="I182" s="3" t="inlineStr">
+        <is>
+          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>Answer rule accepts or rejects</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Q23</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>Q23 | Any final comments? | text | — | Validate: {"max_length": 1000}
+Optional</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>TC-40e56a8b6b</t>
+        </is>
+      </c>
+      <c r="F183" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q23 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at most 1000 characters</t>
+        </is>
+      </c>
+      <c r="G183" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
+3. S3 = No
+4. S4 = No
+5. Q1 = Auto Brand A
+6. Q2 = Auto Brand A
+7. Q3 = Auto Brand A
+8. Q4 = Initial research
+9. Q5 = Manufacturer website
+10. Q6 = Manufacturer website
+11. Q7 = Very poor
+12. Q8 = 0
+13. Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor...
+14. Q10 = Yes
+15. Q11 = Phone
+16. Q12 = Fully
+17. Q13 = Very low
+18. Q15 = Yes
+19. Q16 = Price
+20. Q18 = Price=20; Quality=20; Convenience=20...
+21. Q19 = Concept A
+22. Q20 = Very poor
+23. Q21 = xxxxx
+24. D1 = North
+25. D2 = 21-29
+26. D3 = Woman
+27. D4 = Band 1
+28. Q22 = Yes</t>
+        </is>
+      </c>
+      <c r="H183" s="3" t="inlineStr">
+        <is>
+          <t>At Q23, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
+        </is>
+      </c>
+      <c r="I183" s="3" t="inlineStr">
+        <is>
+          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>Answer rule accepts or rejects</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Q23</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>Q23 | Any final comments? | text | — | Validate: {"max_length": 1000}
+Optional</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>TC-38d0f2db08</t>
+        </is>
+      </c>
+      <c r="F184" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q23 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question</t>
+        </is>
+      </c>
+      <c r="G184" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
+3. S3 = No
+4. S4 = No
+5. Q1 = Auto Brand A
+6. Q2 = Auto Brand A
+7. Q3 = Auto Brand A
+8. Q4 = Initial research
+9. Q5 = Manufacturer website
+10. Q6 = Manufacturer website
+11. Q7 = Very poor
+12. Q8 = 0
+13. Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor...
+14. Q10 = Yes
+15. Q11 = Phone
+16. Q12 = Fully
+17. Q13 = Very low
+18. Q15 = Yes
+19. Q16 = Price
+20. Q18 = Price=20; Quality=20; Convenience=20...
+21. Q19 = Concept A
+22. Q20 = Very poor
+23. Q21 = xxxxx
+24. D1 = North
+25. D2 = 21-29
+26. D3 = Woman
+27. D4 = Band 1
+28. Q22 = Yes</t>
+        </is>
+      </c>
+      <c r="H184" s="3" t="inlineStr">
+        <is>
+          <t>At Q23, type 3 spaces and nothing else, then submit.</t>
+        </is>
+      </c>
+      <c r="I184" s="3" t="inlineStr">
+        <is>
+          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>Blank answer is blocked</t>
+        </is>
+      </c>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>whole survey</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr"/>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>TC-236280087d</t>
+        </is>
+      </c>
+      <c r="F185" s="3" t="inlineStr">
+        <is>
+          <t>Prove the survey finishes normally for a respondent who answers everything and triggers no screen-out</t>
+        </is>
+      </c>
+      <c r="G185" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Purchased or seriously considered a new vehicle in the past 18 months
+3. S3 = No
+4. S4 = No
+5. Q1 = Auto Brand A
+6. Q2 = Auto Brand A
+7. Q3 = Auto Brand A
+8. Q4 = Initial research
+9. Q5 = Manufacturer website
+10. Q6 = Manufacturer website
+11. Q7 = Very poor
+12. Q8 = 0
+13. Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor...
+14. Q10 = Yes
+15. Q11 = Phone
+16. Q12 = Fully
+17. Q13 = Very low
+18. Q15 = Yes
+19. Q16 = Price
+20. Q18 = Price=20; Quality=20; Convenience=20...
+21. Q19 = Concept A
+22. Q20 = Very poor
+23. Q21 = xxxxx
+24. D1 = North
+25. D2 = 21-29
+26. D3 = Woman
+27. D4 = Band 1
+28. Q22 = Yes</t>
+        </is>
+      </c>
+      <c r="H185" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I163" s="3" t="inlineStr">
+      <c r="I185" s="3" t="inlineStr">
         <is>
           <t>1. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
-      <c r="J163" s="2" t="inlineStr">
+      <c r="J185" s="2" t="inlineStr">
         <is>
           <t>Survey ends in the right place</t>
         </is>
       </c>
-      <c r="K163" s="2" t="inlineStr">
+      <c r="K185" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
